--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,410 +656,422 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2417000</v>
+        <v>3098600</v>
       </c>
       <c r="E8" s="3">
-        <v>2691500</v>
+        <v>2453400</v>
       </c>
       <c r="F8" s="3">
-        <v>3514400</v>
+        <v>2732000</v>
       </c>
       <c r="G8" s="3">
-        <v>2898900</v>
+        <v>3567300</v>
       </c>
       <c r="H8" s="3">
-        <v>2718400</v>
+        <v>2942600</v>
       </c>
       <c r="I8" s="3">
-        <v>2326300</v>
+        <v>2759400</v>
       </c>
       <c r="J8" s="3">
+        <v>2361300</v>
+      </c>
+      <c r="K8" s="3">
         <v>3069000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2457000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2346600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2613400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3233100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2749900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2778900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2564100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4456900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3633800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3545400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3213100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4806500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3837100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3198800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3125000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2268700</v>
+        <v>2408700</v>
       </c>
       <c r="E9" s="3">
-        <v>2252600</v>
+        <v>2302900</v>
       </c>
       <c r="F9" s="3">
-        <v>2936800</v>
+        <v>2286500</v>
       </c>
       <c r="G9" s="3">
-        <v>2190200</v>
+        <v>2981000</v>
       </c>
       <c r="H9" s="3">
-        <v>2169200</v>
+        <v>2223200</v>
       </c>
       <c r="I9" s="3">
-        <v>1945300</v>
+        <v>2201800</v>
       </c>
       <c r="J9" s="3">
+        <v>1974600</v>
+      </c>
+      <c r="K9" s="3">
         <v>2645300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1965700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1960400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2140300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2819800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2277000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2419600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2374400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3671300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2955100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3016900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2761100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4003100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3097700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2730600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2618400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>148200</v>
+        <v>689900</v>
       </c>
       <c r="E10" s="3">
-        <v>438900</v>
+        <v>150500</v>
       </c>
       <c r="F10" s="3">
-        <v>577600</v>
+        <v>445500</v>
       </c>
       <c r="G10" s="3">
-        <v>708700</v>
+        <v>586300</v>
       </c>
       <c r="H10" s="3">
-        <v>549200</v>
+        <v>719400</v>
       </c>
       <c r="I10" s="3">
-        <v>381000</v>
+        <v>557500</v>
       </c>
       <c r="J10" s="3">
+        <v>386700</v>
+      </c>
+      <c r="K10" s="3">
         <v>423600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>491400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>386200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>473100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>413200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>472900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>359300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>189700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>785600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>678700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>528500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>452100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>803400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>739500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>468200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>506600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>600700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>704100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>533500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>462600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>662000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>561100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,8 +1104,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1115,77 +1128,80 @@
       <c r="I12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3">
         <v>101800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>82100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>78900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>65300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>107800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>78500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>84900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>69500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>143000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>115100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>116000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>101800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>147100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>115000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>101400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>93800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>129900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>94100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>101300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>85500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>113200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>90400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1276,8 +1292,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,38 +1318,38 @@
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="3">
         <v>9100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>110500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>30500</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>21700</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
@@ -1347,14 +1366,14 @@
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>116000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
@@ -1368,8 +1387,11 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1460,8 +1482,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1491,192 +1516,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2703200</v>
+        <v>2872200</v>
       </c>
       <c r="E17" s="3">
-        <v>2623400</v>
+        <v>2743900</v>
       </c>
       <c r="F17" s="3">
-        <v>3504700</v>
+        <v>2662900</v>
       </c>
       <c r="G17" s="3">
-        <v>2566600</v>
+        <v>3557400</v>
       </c>
       <c r="H17" s="3">
-        <v>2544200</v>
+        <v>2605200</v>
       </c>
       <c r="I17" s="3">
-        <v>2295800</v>
+        <v>2582500</v>
       </c>
       <c r="J17" s="3">
+        <v>2330400</v>
+      </c>
+      <c r="K17" s="3">
         <v>3058200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2380700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2353200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2477100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3354700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2617100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2818900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2740400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4183100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3452300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3475600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3203200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4545400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3569100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3186200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3060400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-286200</v>
+        <v>226400</v>
       </c>
       <c r="E18" s="3">
-        <v>68100</v>
+        <v>-290500</v>
       </c>
       <c r="F18" s="3">
-        <v>9800</v>
+        <v>69100</v>
       </c>
       <c r="G18" s="3">
-        <v>332400</v>
+        <v>9900</v>
       </c>
       <c r="H18" s="3">
-        <v>174200</v>
+        <v>337400</v>
       </c>
       <c r="I18" s="3">
-        <v>30500</v>
+        <v>176800</v>
       </c>
       <c r="J18" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K18" s="3">
         <v>10800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>136300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-121600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>132800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-176200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>273800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>181500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>69800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>261100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>268000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>64600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>102000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>141900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>101300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>44400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>204800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>127600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1709,192 +1741,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-42100</v>
+        <v>-114900</v>
       </c>
       <c r="E20" s="3">
-        <v>31300</v>
+        <v>-42700</v>
       </c>
       <c r="F20" s="3">
-        <v>-21600</v>
+        <v>31800</v>
       </c>
       <c r="G20" s="3">
-        <v>-92100</v>
+        <v>-21900</v>
       </c>
       <c r="H20" s="3">
-        <v>-5900</v>
+        <v>-93500</v>
       </c>
       <c r="I20" s="3">
-        <v>39900</v>
+        <v>-6000</v>
       </c>
       <c r="J20" s="3">
+        <v>40500</v>
+      </c>
+      <c r="K20" s="3">
         <v>14100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>17900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>21700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>64600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-45800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-62200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-41800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-79300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-73400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-82700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>10800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>98500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-181300</v>
+        <v>229400</v>
       </c>
       <c r="E21" s="3">
-        <v>241400</v>
+        <v>-184000</v>
       </c>
       <c r="F21" s="3">
-        <v>130300</v>
+        <v>245000</v>
       </c>
       <c r="G21" s="3">
-        <v>362400</v>
+        <v>132200</v>
       </c>
       <c r="H21" s="3">
-        <v>291600</v>
+        <v>367900</v>
       </c>
       <c r="I21" s="3">
-        <v>196600</v>
+        <v>296000</v>
       </c>
       <c r="J21" s="3">
+        <v>199600</v>
+      </c>
+      <c r="K21" s="3">
         <v>157900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>204500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>128900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>269200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>252100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>100000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>367600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>258700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>209800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>103200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>325600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>333600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>65900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>218200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>190700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>243500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>218900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>177900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>246600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>341100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1916,261 +1955,270 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>5600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>6100</v>
       </c>
       <c r="AB22" s="3">
         <v>6100</v>
       </c>
       <c r="AC22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AD22" s="3">
         <v>6000</v>
       </c>
       <c r="AE22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>6700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-328300</v>
+        <v>111500</v>
       </c>
       <c r="E23" s="3">
-        <v>99400</v>
+        <v>-333200</v>
       </c>
       <c r="F23" s="3">
-        <v>-11800</v>
+        <v>100900</v>
       </c>
       <c r="G23" s="3">
-        <v>240200</v>
+        <v>-12000</v>
       </c>
       <c r="H23" s="3">
-        <v>168300</v>
+        <v>243900</v>
       </c>
       <c r="I23" s="3">
-        <v>70400</v>
+        <v>170800</v>
       </c>
       <c r="J23" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K23" s="3">
         <v>19200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>68700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>125400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-109900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>133400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-120400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>220700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>110800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>59700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-40200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>172900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>185600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-77500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>77700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>52700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>108900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>87500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>49100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>121200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>219400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-116700</v>
+        <v>40200</v>
       </c>
       <c r="E24" s="3">
-        <v>36600</v>
+        <v>-118500</v>
       </c>
       <c r="F24" s="3">
-        <v>-22200</v>
+        <v>37200</v>
       </c>
       <c r="G24" s="3">
-        <v>45700</v>
+        <v>-22500</v>
       </c>
       <c r="H24" s="3">
-        <v>44500</v>
+        <v>46400</v>
       </c>
       <c r="I24" s="3">
-        <v>31900</v>
+        <v>45200</v>
       </c>
       <c r="J24" s="3">
+        <v>32400</v>
+      </c>
+      <c r="K24" s="3">
         <v>6900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>36100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-76400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-20200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>93700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>30000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>32800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>35700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>51200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>68700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>43200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2261,192 +2309,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-211500</v>
+        <v>71300</v>
       </c>
       <c r="E26" s="3">
-        <v>62700</v>
+        <v>-214700</v>
       </c>
       <c r="F26" s="3">
-        <v>10400</v>
+        <v>63700</v>
       </c>
       <c r="G26" s="3">
-        <v>194500</v>
+        <v>10500</v>
       </c>
       <c r="H26" s="3">
-        <v>123800</v>
+        <v>197400</v>
       </c>
       <c r="I26" s="3">
-        <v>38500</v>
+        <v>125600</v>
       </c>
       <c r="J26" s="3">
+        <v>39100</v>
+      </c>
+      <c r="K26" s="3">
         <v>12300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>87500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>103100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-117600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>127000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>80800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>45500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-73000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>160400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>149900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-52500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>135900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>40200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>74000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>78000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>165300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-215400</v>
+        <v>66500</v>
       </c>
       <c r="E27" s="3">
-        <v>60400</v>
+        <v>-218600</v>
       </c>
       <c r="F27" s="3">
-        <v>3400</v>
+        <v>61300</v>
       </c>
       <c r="G27" s="3">
-        <v>190900</v>
+        <v>3500</v>
       </c>
       <c r="H27" s="3">
-        <v>121500</v>
+        <v>193800</v>
       </c>
       <c r="I27" s="3">
-        <v>36200</v>
+        <v>123400</v>
       </c>
       <c r="J27" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>80700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-38000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>97500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-120700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>122500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>77400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>41500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-75600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>154400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>141400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>23300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>130100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>68500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>73000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>161600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2537,8 +2594,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2629,8 +2689,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2721,8 +2784,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2813,192 +2879,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>42100</v>
+        <v>114900</v>
       </c>
       <c r="E32" s="3">
-        <v>-31300</v>
+        <v>42700</v>
       </c>
       <c r="F32" s="3">
-        <v>21600</v>
+        <v>-31800</v>
       </c>
       <c r="G32" s="3">
-        <v>92100</v>
+        <v>21900</v>
       </c>
       <c r="H32" s="3">
-        <v>5900</v>
+        <v>93500</v>
       </c>
       <c r="I32" s="3">
-        <v>-39900</v>
+        <v>6000</v>
       </c>
       <c r="J32" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-17900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-64600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>45800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>62200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>41800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>79300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>73400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>82700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>42200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>26800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>77600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-215400</v>
+        <v>66500</v>
       </c>
       <c r="E33" s="3">
-        <v>60400</v>
+        <v>-218600</v>
       </c>
       <c r="F33" s="3">
-        <v>3400</v>
+        <v>61300</v>
       </c>
       <c r="G33" s="3">
-        <v>190900</v>
+        <v>3500</v>
       </c>
       <c r="H33" s="3">
-        <v>121500</v>
+        <v>193800</v>
       </c>
       <c r="I33" s="3">
-        <v>36200</v>
+        <v>123400</v>
       </c>
       <c r="J33" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K33" s="3">
         <v>6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>80700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>97500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-120700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>122500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>77400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>41500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-75600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>154400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>141400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>23300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>130100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>68500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>73000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>161600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3089,197 +3164,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-215400</v>
+        <v>66500</v>
       </c>
       <c r="E35" s="3">
-        <v>60400</v>
+        <v>-218600</v>
       </c>
       <c r="F35" s="3">
-        <v>3400</v>
+        <v>61300</v>
       </c>
       <c r="G35" s="3">
-        <v>190900</v>
+        <v>3500</v>
       </c>
       <c r="H35" s="3">
-        <v>121500</v>
+        <v>193800</v>
       </c>
       <c r="I35" s="3">
-        <v>36200</v>
+        <v>123400</v>
       </c>
       <c r="J35" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K35" s="3">
         <v>6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>80700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>97500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-120700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>122500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>77400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>41500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-75600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>154400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>141400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>23300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>130100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>68500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>73000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>161600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3312,8 +3396,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3346,126 +3431,130 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>567100</v>
+        <v>687600</v>
       </c>
       <c r="E41" s="3">
-        <v>610100</v>
+        <v>575700</v>
       </c>
       <c r="F41" s="3">
-        <v>919100</v>
+        <v>619300</v>
       </c>
       <c r="G41" s="3">
-        <v>584300</v>
+        <v>933000</v>
       </c>
       <c r="H41" s="3">
-        <v>551400</v>
+        <v>593100</v>
       </c>
       <c r="I41" s="3">
-        <v>521200</v>
+        <v>559700</v>
       </c>
       <c r="J41" s="3">
+        <v>529100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1480600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>517000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>436900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>897100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>898300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1006600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1193300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1464500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>934800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>677900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>383600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>407000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>714100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>473500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>533400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>527700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>638500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>455700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>410800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>436300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>491300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>474100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>71100</v>
+        <v>92700</v>
       </c>
       <c r="E42" s="3">
-        <v>61600</v>
+        <v>72200</v>
       </c>
       <c r="F42" s="3">
-        <v>71300</v>
+        <v>62500</v>
       </c>
       <c r="G42" s="3">
-        <v>96800</v>
+        <v>72400</v>
       </c>
       <c r="H42" s="3">
-        <v>58000</v>
+        <v>98300</v>
       </c>
       <c r="I42" s="3">
-        <v>83500</v>
+        <v>58900</v>
       </c>
       <c r="J42" s="3">
+        <v>84800</v>
+      </c>
+      <c r="K42" s="3">
         <v>70400</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
@@ -3479,8 +3568,8 @@
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3530,402 +3619,417 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4250300</v>
+        <v>4700300</v>
       </c>
       <c r="E43" s="3">
-        <v>4150400</v>
+        <v>4314300</v>
       </c>
       <c r="F43" s="3">
-        <v>4185700</v>
+        <v>4212900</v>
       </c>
       <c r="G43" s="3">
-        <v>4121300</v>
+        <v>4248700</v>
       </c>
       <c r="H43" s="3">
-        <v>3716900</v>
+        <v>4183300</v>
       </c>
       <c r="I43" s="3">
-        <v>3486200</v>
+        <v>3772900</v>
       </c>
       <c r="J43" s="3">
+        <v>3538700</v>
+      </c>
+      <c r="K43" s="3">
         <v>6216000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3048600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2986800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3239000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3474100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3362100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3641000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4139300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4957300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4749700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4250400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4073400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5283800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4529800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4362500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5002200</v>
+        <v>5236600</v>
       </c>
       <c r="E44" s="3">
-        <v>4775400</v>
+        <v>5077600</v>
       </c>
       <c r="F44" s="3">
-        <v>4584500</v>
+        <v>4847300</v>
       </c>
       <c r="G44" s="3">
-        <v>4843700</v>
+        <v>4653500</v>
       </c>
       <c r="H44" s="3">
-        <v>4664000</v>
+        <v>4916700</v>
       </c>
       <c r="I44" s="3">
-        <v>4389200</v>
+        <v>4734200</v>
       </c>
       <c r="J44" s="3">
+        <v>4455300</v>
+      </c>
+      <c r="K44" s="3">
         <v>8460400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4786300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4723100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4566000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4669100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5015600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5136400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5615900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5564900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6074600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5759800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5787500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5697000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6032500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5635200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5097500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>758600</v>
+        <v>812100</v>
       </c>
       <c r="E45" s="3">
-        <v>811300</v>
+        <v>770000</v>
       </c>
       <c r="F45" s="3">
-        <v>666600</v>
+        <v>823500</v>
       </c>
       <c r="G45" s="3">
-        <v>779300</v>
+        <v>676600</v>
       </c>
       <c r="H45" s="3">
-        <v>703300</v>
+        <v>791000</v>
       </c>
       <c r="I45" s="3">
-        <v>696400</v>
+        <v>713800</v>
       </c>
       <c r="J45" s="3">
+        <v>706900</v>
+      </c>
+      <c r="K45" s="3">
         <v>1156000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>815400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>741800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>571100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>307100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>499700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>442900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>528600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>450900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>604200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>561800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>592100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>435700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>816100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>761300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>773600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>655800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>847500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>969300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10649300</v>
+        <v>11529200</v>
       </c>
       <c r="E46" s="3">
-        <v>10408800</v>
+        <v>10809700</v>
       </c>
       <c r="F46" s="3">
-        <v>10427100</v>
+        <v>10565500</v>
       </c>
       <c r="G46" s="3">
-        <v>10425400</v>
+        <v>10584200</v>
       </c>
       <c r="H46" s="3">
-        <v>9693500</v>
+        <v>10582400</v>
       </c>
       <c r="I46" s="3">
-        <v>9176500</v>
+        <v>9839500</v>
       </c>
       <c r="J46" s="3">
+        <v>9314700</v>
+      </c>
+      <c r="K46" s="3">
         <v>8766200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9167300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8802400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9020900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9113500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9995900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10134700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11250000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11089900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12314000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11454800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11037000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10920200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12605900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11459600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10761400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1124100</v>
+        <v>1134900</v>
       </c>
       <c r="E47" s="3">
-        <v>1078400</v>
+        <v>1141000</v>
       </c>
       <c r="F47" s="3">
-        <v>980500</v>
+        <v>1094600</v>
       </c>
       <c r="G47" s="3">
-        <v>992600</v>
+        <v>995300</v>
       </c>
       <c r="H47" s="3">
-        <v>997200</v>
+        <v>1007600</v>
       </c>
       <c r="I47" s="3">
-        <v>984700</v>
+        <v>1012200</v>
       </c>
       <c r="J47" s="3">
+        <v>999500</v>
+      </c>
+      <c r="K47" s="3">
         <v>928400</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
@@ -3990,192 +4094,201 @@
       <c r="AF47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3589700</v>
+        <v>3694600</v>
       </c>
       <c r="E48" s="3">
-        <v>3513100</v>
+        <v>3643700</v>
       </c>
       <c r="F48" s="3">
-        <v>3449000</v>
+        <v>3566000</v>
       </c>
       <c r="G48" s="3">
-        <v>3371700</v>
+        <v>3501000</v>
       </c>
       <c r="H48" s="3">
-        <v>3389000</v>
+        <v>3422500</v>
       </c>
       <c r="I48" s="3">
-        <v>3365500</v>
+        <v>3440100</v>
       </c>
       <c r="J48" s="3">
+        <v>3416200</v>
+      </c>
+      <c r="K48" s="3">
         <v>6289100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3037000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3209100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3284500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3199400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3395700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3631100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4025000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4251400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4416300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4465200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4457200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4667300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4563000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4490400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4389800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>452300</v>
+        <v>459200</v>
       </c>
       <c r="E49" s="3">
-        <v>456000</v>
+        <v>459100</v>
       </c>
       <c r="F49" s="3">
-        <v>439900</v>
+        <v>462900</v>
       </c>
       <c r="G49" s="3">
-        <v>413600</v>
+        <v>446500</v>
       </c>
       <c r="H49" s="3">
-        <v>411600</v>
+        <v>419900</v>
       </c>
       <c r="I49" s="3">
-        <v>409000</v>
+        <v>417800</v>
       </c>
       <c r="J49" s="3">
+        <v>415200</v>
+      </c>
+      <c r="K49" s="3">
         <v>411300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>151800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>159400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>162400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>159000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>161900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>173300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>187600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>188200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>172900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>172200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>163500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>161400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>153300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>149800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>147200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>146200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>139900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>140700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>135000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>135600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>129900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4266,8 +4379,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4358,100 +4474,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1159600</v>
+        <v>1132100</v>
       </c>
       <c r="E52" s="3">
-        <v>1016000</v>
+        <v>1177100</v>
       </c>
       <c r="F52" s="3">
-        <v>1022800</v>
+        <v>1031300</v>
       </c>
       <c r="G52" s="3">
-        <v>974600</v>
+        <v>1038200</v>
       </c>
       <c r="H52" s="3">
-        <v>992000</v>
+        <v>989300</v>
       </c>
       <c r="I52" s="3">
-        <v>983500</v>
+        <v>1007000</v>
       </c>
       <c r="J52" s="3">
+        <v>998300</v>
+      </c>
+      <c r="K52" s="3">
         <v>2702900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1706800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1826200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1903300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1457600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1421800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1488900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1726200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1735300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1816600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1839200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1865000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1936100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1603200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1588900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1530100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4542,100 +4664,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16975000</v>
+        <v>17950000</v>
       </c>
       <c r="E54" s="3">
-        <v>16472300</v>
+        <v>17230700</v>
       </c>
       <c r="F54" s="3">
-        <v>16319300</v>
+        <v>16720400</v>
       </c>
       <c r="G54" s="3">
-        <v>16178000</v>
+        <v>16565100</v>
       </c>
       <c r="H54" s="3">
-        <v>15483300</v>
+        <v>16421600</v>
       </c>
       <c r="I54" s="3">
-        <v>14919200</v>
+        <v>15716500</v>
       </c>
       <c r="J54" s="3">
+        <v>15143900</v>
+      </c>
+      <c r="K54" s="3">
         <v>14439500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14053900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13987200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14360900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13919600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14965300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15415400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17173200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17248600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18707700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17918500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17509700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17671400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18892700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17656100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16797100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4668,8 +4796,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4702,560 +4831,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3030600</v>
+        <v>3211600</v>
       </c>
       <c r="E57" s="3">
-        <v>2900500</v>
+        <v>3076200</v>
       </c>
       <c r="F57" s="3">
-        <v>3002900</v>
+        <v>2944200</v>
       </c>
       <c r="G57" s="3">
-        <v>2876000</v>
+        <v>3048200</v>
       </c>
       <c r="H57" s="3">
-        <v>2642000</v>
+        <v>2919300</v>
       </c>
       <c r="I57" s="3">
-        <v>2510600</v>
+        <v>2681800</v>
       </c>
       <c r="J57" s="3">
+        <v>2548400</v>
+      </c>
+      <c r="K57" s="3">
         <v>4941500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2174500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2173700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2313900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2518000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2447800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2367500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2621900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3274500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3083100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2942400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3095300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3558300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3258700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3116400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3052900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3125600</v>
+        <v>3855600</v>
       </c>
       <c r="E58" s="3">
-        <v>2720900</v>
+        <v>3172600</v>
       </c>
       <c r="F58" s="3">
-        <v>2139700</v>
+        <v>2761900</v>
       </c>
       <c r="G58" s="3">
-        <v>2740700</v>
+        <v>2172000</v>
       </c>
       <c r="H58" s="3">
-        <v>2411700</v>
+        <v>2782000</v>
       </c>
       <c r="I58" s="3">
-        <v>2154800</v>
+        <v>2448000</v>
       </c>
       <c r="J58" s="3">
+        <v>2187200</v>
+      </c>
+      <c r="K58" s="3">
         <v>3378000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1223400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1279500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1016400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1224000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1345800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1415400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1634900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1653900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2582000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1721200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1287200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1060400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2197400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1264300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1106800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>976200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3674900</v>
+        <v>3459800</v>
       </c>
       <c r="E59" s="3">
-        <v>3319200</v>
+        <v>3730200</v>
       </c>
       <c r="F59" s="3">
-        <v>3546800</v>
+        <v>3369200</v>
       </c>
       <c r="G59" s="3">
-        <v>3029400</v>
+        <v>3600200</v>
       </c>
       <c r="H59" s="3">
-        <v>3002800</v>
+        <v>3075000</v>
       </c>
       <c r="I59" s="3">
-        <v>2997500</v>
+        <v>3048000</v>
       </c>
       <c r="J59" s="3">
+        <v>3042600</v>
+      </c>
+      <c r="K59" s="3">
         <v>4901600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3758300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3306200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3568900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2763500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3549100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3645000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3728900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3421000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4249500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4400600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4389200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3687000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4536000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4683500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4229300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9831000</v>
+        <v>10526900</v>
       </c>
       <c r="E60" s="3">
-        <v>8940600</v>
+        <v>9979100</v>
       </c>
       <c r="F60" s="3">
-        <v>8689500</v>
+        <v>9075300</v>
       </c>
       <c r="G60" s="3">
-        <v>8646100</v>
+        <v>8820400</v>
       </c>
       <c r="H60" s="3">
-        <v>8056400</v>
+        <v>8776300</v>
       </c>
       <c r="I60" s="3">
-        <v>7662800</v>
+        <v>8177700</v>
       </c>
       <c r="J60" s="3">
+        <v>7778200</v>
+      </c>
+      <c r="K60" s="3">
         <v>7036600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7156200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6759400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6899100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6505500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7342700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7428000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7985700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8349500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9914600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9064200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8771700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8305700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9992100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9064200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8389000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2535600</v>
+        <v>2691700</v>
       </c>
       <c r="E61" s="3">
-        <v>2773400</v>
+        <v>2573800</v>
       </c>
       <c r="F61" s="3">
-        <v>2906700</v>
+        <v>2815200</v>
       </c>
       <c r="G61" s="3">
-        <v>2856500</v>
+        <v>2950500</v>
       </c>
       <c r="H61" s="3">
-        <v>2873100</v>
+        <v>2899500</v>
       </c>
       <c r="I61" s="3">
-        <v>2853400</v>
+        <v>2916400</v>
       </c>
       <c r="J61" s="3">
+        <v>2896400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2978600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2553900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2705600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2831300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2826800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2831300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3012800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3572900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3081100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3024000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3087500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2996100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3162500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2995400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2840900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2830800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>745600</v>
+        <v>759400</v>
       </c>
       <c r="E62" s="3">
-        <v>739400</v>
+        <v>756800</v>
       </c>
       <c r="F62" s="3">
-        <v>759800</v>
+        <v>750500</v>
       </c>
       <c r="G62" s="3">
-        <v>842200</v>
+        <v>771300</v>
       </c>
       <c r="H62" s="3">
-        <v>842400</v>
+        <v>854800</v>
       </c>
       <c r="I62" s="3">
-        <v>831800</v>
+        <v>855100</v>
       </c>
       <c r="J62" s="3">
+        <v>844300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1233200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1200600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1262100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1277500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1164400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1444200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1537400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1711600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1663500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1441800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1418300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1393600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1472600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1362100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1360700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1236500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5346,8 +5494,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5438,8 +5589,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5530,100 +5684,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13244500</v>
+        <v>14116400</v>
       </c>
       <c r="E66" s="3">
-        <v>12589500</v>
+        <v>13443900</v>
       </c>
       <c r="F66" s="3">
-        <v>12493300</v>
+        <v>12779100</v>
       </c>
       <c r="G66" s="3">
-        <v>12466900</v>
+        <v>12681500</v>
       </c>
       <c r="H66" s="3">
-        <v>11894800</v>
+        <v>12654600</v>
       </c>
       <c r="I66" s="3">
-        <v>11467700</v>
+        <v>12074000</v>
       </c>
       <c r="J66" s="3">
+        <v>11640400</v>
+      </c>
+      <c r="K66" s="3">
         <v>11083100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11040200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10858200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11138400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10620400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11739800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12100800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13401500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13234500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14525700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13713800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13304000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13093300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14506700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13411300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12591200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5656,8 +5816,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5748,8 +5909,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5840,8 +6004,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5932,8 +6099,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6024,100 +6194,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2302900</v>
+        <v>2380000</v>
       </c>
       <c r="E72" s="3">
-        <v>2518700</v>
+        <v>2337500</v>
       </c>
       <c r="F72" s="3">
-        <v>2524900</v>
+        <v>2556600</v>
       </c>
       <c r="G72" s="3">
-        <v>2425600</v>
+        <v>2562900</v>
       </c>
       <c r="H72" s="3">
-        <v>2269200</v>
+        <v>2462100</v>
       </c>
       <c r="I72" s="3">
-        <v>2146500</v>
+        <v>2303400</v>
       </c>
       <c r="J72" s="3">
+        <v>2178900</v>
+      </c>
+      <c r="K72" s="3">
         <v>2129300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1860900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1957200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2034500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2173600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2286100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2332000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2685700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2877600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2848900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2849600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2798900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3119500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2912600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2781500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2777500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6208,8 +6384,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6300,8 +6479,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6392,100 +6574,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3730500</v>
+        <v>3833600</v>
       </c>
       <c r="E76" s="3">
-        <v>3882900</v>
+        <v>3786700</v>
       </c>
       <c r="F76" s="3">
-        <v>3826000</v>
+        <v>3941300</v>
       </c>
       <c r="G76" s="3">
-        <v>3711100</v>
+        <v>3883600</v>
       </c>
       <c r="H76" s="3">
-        <v>3588500</v>
+        <v>3767000</v>
       </c>
       <c r="I76" s="3">
-        <v>3451500</v>
+        <v>3642500</v>
       </c>
       <c r="J76" s="3">
+        <v>3503500</v>
+      </c>
+      <c r="K76" s="3">
         <v>3356400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3013700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3128900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3222500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3299200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3225400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3314600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3771700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4014100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4182100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4204800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4205800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4578100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4386000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4244700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4205900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6576,197 +6764,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-215400</v>
+        <v>66500</v>
       </c>
       <c r="E81" s="3">
-        <v>60400</v>
+        <v>-218600</v>
       </c>
       <c r="F81" s="3">
-        <v>3400</v>
+        <v>61300</v>
       </c>
       <c r="G81" s="3">
-        <v>190900</v>
+        <v>3500</v>
       </c>
       <c r="H81" s="3">
-        <v>121500</v>
+        <v>193800</v>
       </c>
       <c r="I81" s="3">
-        <v>36200</v>
+        <v>123400</v>
       </c>
       <c r="J81" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K81" s="3">
         <v>6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>80700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>97500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-120700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>122500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>77400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>41500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-75600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>154400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>141400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>23300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>130100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>68500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>73000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>161600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6799,100 +6996,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>147000</v>
+        <v>117900</v>
       </c>
       <c r="E83" s="3">
-        <v>142000</v>
+        <v>149200</v>
       </c>
       <c r="F83" s="3">
-        <v>142100</v>
+        <v>144200</v>
       </c>
       <c r="G83" s="3">
-        <v>122200</v>
+        <v>144200</v>
       </c>
       <c r="H83" s="3">
-        <v>123300</v>
+        <v>124000</v>
       </c>
       <c r="I83" s="3">
-        <v>126200</v>
+        <v>125200</v>
       </c>
       <c r="J83" s="3">
+        <v>128100</v>
+      </c>
+      <c r="K83" s="3">
         <v>133000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>130100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>139400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>137300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>112000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>111700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>118200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>128300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>139600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>139400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>141400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>135100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>143800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>139000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>136000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>133600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>130900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>128500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>125300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>122800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>119500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>115100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6983,8 +7184,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7075,8 +7279,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7167,8 +7374,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7259,8 +7469,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7351,49 +7564,52 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>46400</v>
+        <v>-555900</v>
       </c>
       <c r="E89" s="3">
-        <v>-149000</v>
+        <v>47100</v>
       </c>
       <c r="F89" s="3">
-        <v>907900</v>
+        <v>-151200</v>
       </c>
       <c r="G89" s="3">
-        <v>-286100</v>
+        <v>921600</v>
       </c>
       <c r="H89" s="3">
-        <v>-53400</v>
+        <v>-290400</v>
       </c>
       <c r="I89" s="3">
-        <v>-411600</v>
+        <v>-54200</v>
       </c>
       <c r="J89" s="3">
+        <v>-417800</v>
+      </c>
+      <c r="K89" s="3">
         <v>1942400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-353600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-393600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-217400</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -7443,8 +7659,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7477,49 +7696,50 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32106000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29437000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19019000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31195000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-103000</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7569,8 +7789,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7661,8 +7884,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7753,49 +7979,52 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-173300</v>
+        <v>-222500</v>
       </c>
       <c r="E94" s="3">
-        <v>-146000</v>
+        <v>-175900</v>
       </c>
       <c r="F94" s="3">
-        <v>-160600</v>
+        <v>-148200</v>
       </c>
       <c r="G94" s="3">
-        <v>-118300</v>
+        <v>-163000</v>
       </c>
       <c r="H94" s="3">
-        <v>-75800</v>
+        <v>-120100</v>
       </c>
       <c r="I94" s="3">
-        <v>-159600</v>
+        <v>-76900</v>
       </c>
       <c r="J94" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-40400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-125500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-105300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-99800</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7845,8 +8074,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7879,44 +8111,45 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4700</v>
+        <v>-21300</v>
       </c>
       <c r="E96" s="3">
-        <v>-61900</v>
+        <v>-4800</v>
       </c>
       <c r="F96" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="G96" s="3">
         <v>-2700</v>
       </c>
-      <c r="G96" s="3">
-        <v>-30700</v>
-      </c>
       <c r="H96" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I96" s="3">
         <v>-1800</v>
       </c>
-      <c r="I96" s="3">
-        <v>-20500</v>
-      </c>
       <c r="J96" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-21300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -7971,8 +8204,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8063,8 +8299,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8155,8 +8394,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8247,49 +8489,52 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>104100</v>
+        <v>870400</v>
       </c>
       <c r="E100" s="3">
-        <v>12800</v>
+        <v>105700</v>
       </c>
       <c r="F100" s="3">
-        <v>-439900</v>
+        <v>13000</v>
       </c>
       <c r="G100" s="3">
-        <v>400700</v>
+        <v>-446600</v>
       </c>
       <c r="H100" s="3">
-        <v>188900</v>
+        <v>406700</v>
       </c>
       <c r="I100" s="3">
-        <v>416800</v>
+        <v>191700</v>
       </c>
       <c r="J100" s="3">
+        <v>423100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>510300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>128200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>277100</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -8339,49 +8584,52 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-20100</v>
+        <v>19900</v>
       </c>
       <c r="E101" s="3">
-        <v>-26800</v>
+        <v>-20400</v>
       </c>
       <c r="F101" s="3">
-        <v>27400</v>
+        <v>-27200</v>
       </c>
       <c r="G101" s="3">
-        <v>36600</v>
+        <v>27900</v>
       </c>
       <c r="H101" s="3">
-        <v>-29500</v>
+        <v>37100</v>
       </c>
       <c r="I101" s="3">
-        <v>-44800</v>
+        <v>-30000</v>
       </c>
       <c r="J101" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-13400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2600</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8431,49 +8679,52 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-42900</v>
+        <v>111900</v>
       </c>
       <c r="E102" s="3">
-        <v>-309000</v>
+        <v>-43600</v>
       </c>
       <c r="F102" s="3">
-        <v>334800</v>
+        <v>-313700</v>
       </c>
       <c r="G102" s="3">
-        <v>32900</v>
+        <v>339800</v>
       </c>
       <c r="H102" s="3">
-        <v>30200</v>
+        <v>33400</v>
       </c>
       <c r="I102" s="3">
-        <v>-199300</v>
+        <v>30700</v>
       </c>
       <c r="J102" s="3">
+        <v>-202300</v>
+      </c>
+      <c r="K102" s="3">
         <v>264600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>95400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-449100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-37500</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -8521,6 +8772,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,422 +656,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3098600</v>
+        <v>3957000</v>
       </c>
       <c r="E8" s="3">
-        <v>2453400</v>
+        <v>2933100</v>
       </c>
       <c r="F8" s="3">
-        <v>2732000</v>
+        <v>2322300</v>
       </c>
       <c r="G8" s="3">
-        <v>3567300</v>
+        <v>2586100</v>
       </c>
       <c r="H8" s="3">
-        <v>2942600</v>
+        <v>3376800</v>
       </c>
       <c r="I8" s="3">
-        <v>2759400</v>
+        <v>2785400</v>
       </c>
       <c r="J8" s="3">
+        <v>2612000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2361300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3069000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2457000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2346600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2613400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3233100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2749900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2778900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2564100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4456900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3633800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3545400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3213100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4806500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3837100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3198800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2408700</v>
+        <v>3182000</v>
       </c>
       <c r="E9" s="3">
-        <v>2302900</v>
+        <v>2280000</v>
       </c>
       <c r="F9" s="3">
-        <v>2286500</v>
+        <v>2179900</v>
       </c>
       <c r="G9" s="3">
-        <v>2981000</v>
+        <v>2164400</v>
       </c>
       <c r="H9" s="3">
-        <v>2223200</v>
+        <v>2821800</v>
       </c>
       <c r="I9" s="3">
-        <v>2201800</v>
+        <v>2104400</v>
       </c>
       <c r="J9" s="3">
+        <v>2084200</v>
+      </c>
+      <c r="K9" s="3">
         <v>1974600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2645300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1965700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1960400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2140300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2819800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2277000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2419600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2374400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3671300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2955100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3016900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2761100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4003100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3097700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2730600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>689900</v>
+        <v>775000</v>
       </c>
       <c r="E10" s="3">
-        <v>150500</v>
+        <v>653000</v>
       </c>
       <c r="F10" s="3">
-        <v>445500</v>
+        <v>142400</v>
       </c>
       <c r="G10" s="3">
-        <v>586300</v>
+        <v>421700</v>
       </c>
       <c r="H10" s="3">
-        <v>719400</v>
+        <v>555000</v>
       </c>
       <c r="I10" s="3">
-        <v>557500</v>
+        <v>681000</v>
       </c>
       <c r="J10" s="3">
+        <v>527700</v>
+      </c>
+      <c r="K10" s="3">
         <v>386700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>423600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>491400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>386200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>473100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>413200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>472900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>359300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>189700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>785600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>678700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>528500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>452100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>803400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>739500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>468200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>506600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>600700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>704100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>533500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>462600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>662000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>561100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,8 +1117,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1131,77 +1144,80 @@
       <c r="J12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
         <v>101800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>78900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>65300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>107800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>78500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>84900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>69500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>143000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>115100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>116000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>101800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>147100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>115000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>101400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>93800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>129900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>94100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>101300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>85500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>113200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>90400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1295,8 +1311,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,38 +1340,38 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
         <v>9100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>110500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>30500</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>21700</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
@@ -1369,14 +1388,14 @@
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>116000</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1390,8 +1409,11 @@
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1485,8 +1507,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1517,198 +1542,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2872200</v>
+        <v>3667000</v>
       </c>
       <c r="E17" s="3">
-        <v>2743900</v>
+        <v>2718800</v>
       </c>
       <c r="F17" s="3">
-        <v>2662900</v>
+        <v>2597300</v>
       </c>
       <c r="G17" s="3">
-        <v>3557400</v>
+        <v>2520700</v>
       </c>
       <c r="H17" s="3">
-        <v>2605200</v>
+        <v>3367400</v>
       </c>
       <c r="I17" s="3">
-        <v>2582500</v>
+        <v>2466100</v>
       </c>
       <c r="J17" s="3">
+        <v>2444600</v>
+      </c>
+      <c r="K17" s="3">
         <v>2330400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3058200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2380700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2353200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2477100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3354700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2617100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2818900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2740400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4183100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3452300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3475600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3203200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4545400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3569100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3186200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>226400</v>
+        <v>290000</v>
       </c>
       <c r="E18" s="3">
-        <v>-290500</v>
+        <v>214300</v>
       </c>
       <c r="F18" s="3">
-        <v>69100</v>
+        <v>-275000</v>
       </c>
       <c r="G18" s="3">
-        <v>9900</v>
+        <v>65400</v>
       </c>
       <c r="H18" s="3">
-        <v>337400</v>
+        <v>9400</v>
       </c>
       <c r="I18" s="3">
-        <v>176800</v>
+        <v>319300</v>
       </c>
       <c r="J18" s="3">
+        <v>167400</v>
+      </c>
+      <c r="K18" s="3">
         <v>31000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>76300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>136300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-121600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>132800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-176200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>273800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>181500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>69800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>261100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>268000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>64600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>102000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>141900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>101300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>44400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>204800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>127600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1742,198 +1774,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-114900</v>
+        <v>28400</v>
       </c>
       <c r="E20" s="3">
-        <v>-42700</v>
+        <v>-108800</v>
       </c>
       <c r="F20" s="3">
-        <v>31800</v>
+        <v>-40400</v>
       </c>
       <c r="G20" s="3">
-        <v>-21900</v>
+        <v>30100</v>
       </c>
       <c r="H20" s="3">
-        <v>-93500</v>
+        <v>-20700</v>
       </c>
       <c r="I20" s="3">
-        <v>-6000</v>
+        <v>-88500</v>
       </c>
       <c r="J20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K20" s="3">
         <v>40500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>17900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>64600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-45800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-62200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-41800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-79300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-73400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-82700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>10800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>98500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>229400</v>
+        <v>445800</v>
       </c>
       <c r="E21" s="3">
-        <v>-184000</v>
+        <v>217100</v>
       </c>
       <c r="F21" s="3">
-        <v>245000</v>
+        <v>-174200</v>
       </c>
       <c r="G21" s="3">
-        <v>132200</v>
+        <v>232000</v>
       </c>
       <c r="H21" s="3">
-        <v>367900</v>
+        <v>125200</v>
       </c>
       <c r="I21" s="3">
-        <v>296000</v>
+        <v>348200</v>
       </c>
       <c r="J21" s="3">
+        <v>280200</v>
+      </c>
+      <c r="K21" s="3">
         <v>199600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>157900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>204500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>128900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>269200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>252100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>100000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>367600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>258700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>209800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>103200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>325600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>333600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>65900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>218200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>190700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>243500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>218900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>177900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>246600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>341100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1958,267 +1997,276 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>5600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>6100</v>
       </c>
       <c r="AC22" s="3">
         <v>6100</v>
       </c>
       <c r="AD22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AE22" s="3">
         <v>6000</v>
       </c>
       <c r="AF22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>6700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>111500</v>
+        <v>318400</v>
       </c>
       <c r="E23" s="3">
-        <v>-333200</v>
+        <v>105500</v>
       </c>
       <c r="F23" s="3">
-        <v>100900</v>
+        <v>-315400</v>
       </c>
       <c r="G23" s="3">
-        <v>-12000</v>
+        <v>95500</v>
       </c>
       <c r="H23" s="3">
-        <v>243900</v>
+        <v>-11300</v>
       </c>
       <c r="I23" s="3">
-        <v>170800</v>
+        <v>230800</v>
       </c>
       <c r="J23" s="3">
+        <v>161700</v>
+      </c>
+      <c r="K23" s="3">
         <v>71500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>68700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>125400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-109900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>133400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-120400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>220700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>110800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>59700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-40200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>172900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>185600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-77500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>77700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>52700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>108900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>87500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>49100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>121200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>219400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>40200</v>
+        <v>68700</v>
       </c>
       <c r="E24" s="3">
-        <v>-118500</v>
+        <v>38100</v>
       </c>
       <c r="F24" s="3">
-        <v>37200</v>
+        <v>-112200</v>
       </c>
       <c r="G24" s="3">
-        <v>-22500</v>
+        <v>35200</v>
       </c>
       <c r="H24" s="3">
-        <v>46400</v>
+        <v>-21300</v>
       </c>
       <c r="I24" s="3">
-        <v>45200</v>
+        <v>43900</v>
       </c>
       <c r="J24" s="3">
+        <v>42800</v>
+      </c>
+      <c r="K24" s="3">
         <v>32400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-76400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>30200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>92100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-20200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>93700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>30000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>32800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>35700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>51200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>68700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>43200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2312,198 +2360,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>71300</v>
+        <v>249800</v>
       </c>
       <c r="E26" s="3">
-        <v>-214700</v>
+        <v>67500</v>
       </c>
       <c r="F26" s="3">
-        <v>63700</v>
+        <v>-203300</v>
       </c>
       <c r="G26" s="3">
-        <v>10500</v>
+        <v>60300</v>
       </c>
       <c r="H26" s="3">
-        <v>197400</v>
+        <v>10000</v>
       </c>
       <c r="I26" s="3">
-        <v>125600</v>
+        <v>186900</v>
       </c>
       <c r="J26" s="3">
+        <v>118900</v>
+      </c>
+      <c r="K26" s="3">
         <v>39100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>87500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>103100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-117600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>127000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>80800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>45500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-73000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>160400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>149900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-52500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>135900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>40200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>74000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>78000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>165300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>66500</v>
+        <v>247900</v>
       </c>
       <c r="E27" s="3">
-        <v>-218600</v>
+        <v>62900</v>
       </c>
       <c r="F27" s="3">
-        <v>61300</v>
+        <v>-206900</v>
       </c>
       <c r="G27" s="3">
-        <v>3500</v>
+        <v>58000</v>
       </c>
       <c r="H27" s="3">
-        <v>193800</v>
+        <v>3300</v>
       </c>
       <c r="I27" s="3">
-        <v>123400</v>
+        <v>183400</v>
       </c>
       <c r="J27" s="3">
+        <v>116800</v>
+      </c>
+      <c r="K27" s="3">
         <v>36800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>80700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>97500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-120700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>122500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>77400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>41500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-75600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>154400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>141400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>130100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>33100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>68500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>29600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>73000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>161600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2597,8 +2654,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2692,8 +2752,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2787,8 +2850,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2882,198 +2948,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>114900</v>
+        <v>-28400</v>
       </c>
       <c r="E32" s="3">
-        <v>42700</v>
+        <v>108800</v>
       </c>
       <c r="F32" s="3">
-        <v>-31800</v>
+        <v>40400</v>
       </c>
       <c r="G32" s="3">
-        <v>21900</v>
+        <v>-30100</v>
       </c>
       <c r="H32" s="3">
-        <v>93500</v>
+        <v>20700</v>
       </c>
       <c r="I32" s="3">
-        <v>6000</v>
+        <v>88500</v>
       </c>
       <c r="J32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-40500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-17900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-64600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>45800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>62200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>41800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>79300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>73400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>82700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>42200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>26800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>77600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>66500</v>
+        <v>247900</v>
       </c>
       <c r="E33" s="3">
-        <v>-218600</v>
+        <v>62900</v>
       </c>
       <c r="F33" s="3">
-        <v>61300</v>
+        <v>-206900</v>
       </c>
       <c r="G33" s="3">
-        <v>3500</v>
+        <v>58000</v>
       </c>
       <c r="H33" s="3">
-        <v>193800</v>
+        <v>3300</v>
       </c>
       <c r="I33" s="3">
-        <v>123400</v>
+        <v>183400</v>
       </c>
       <c r="J33" s="3">
+        <v>116800</v>
+      </c>
+      <c r="K33" s="3">
         <v>36800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>80700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>97500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-120700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>122500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>77400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-75600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>154400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>141400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>130100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>68500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>29600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>73000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>161600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3167,203 +3242,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>66500</v>
+        <v>247900</v>
       </c>
       <c r="E35" s="3">
-        <v>-218600</v>
+        <v>62900</v>
       </c>
       <c r="F35" s="3">
-        <v>61300</v>
+        <v>-206900</v>
       </c>
       <c r="G35" s="3">
-        <v>3500</v>
+        <v>58000</v>
       </c>
       <c r="H35" s="3">
-        <v>193800</v>
+        <v>3300</v>
       </c>
       <c r="I35" s="3">
-        <v>123400</v>
+        <v>183400</v>
       </c>
       <c r="J35" s="3">
+        <v>116800</v>
+      </c>
+      <c r="K35" s="3">
         <v>36800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>80700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>97500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-120700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>122500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>77400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-75600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>154400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>141400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>130100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>68500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>29600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>73000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>161600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3397,8 +3481,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3432,132 +3517,136 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>687600</v>
+        <v>536900</v>
       </c>
       <c r="E41" s="3">
-        <v>575700</v>
+        <v>650900</v>
       </c>
       <c r="F41" s="3">
-        <v>619300</v>
+        <v>544900</v>
       </c>
       <c r="G41" s="3">
-        <v>933000</v>
+        <v>586200</v>
       </c>
       <c r="H41" s="3">
-        <v>593100</v>
+        <v>883100</v>
       </c>
       <c r="I41" s="3">
-        <v>559700</v>
+        <v>561400</v>
       </c>
       <c r="J41" s="3">
+        <v>529800</v>
+      </c>
+      <c r="K41" s="3">
         <v>529100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1480600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>517000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>436900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>897100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>898300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1006600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1193300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1464500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>934800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>677900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>383600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>407000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>714100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>473500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>533400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>527700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>638500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>455700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>410800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>436300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>491300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>474100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>92700</v>
+        <v>70300</v>
       </c>
       <c r="E42" s="3">
-        <v>72200</v>
+        <v>87700</v>
       </c>
       <c r="F42" s="3">
-        <v>62500</v>
+        <v>68300</v>
       </c>
       <c r="G42" s="3">
-        <v>72400</v>
+        <v>59200</v>
       </c>
       <c r="H42" s="3">
-        <v>98300</v>
+        <v>68500</v>
       </c>
       <c r="I42" s="3">
-        <v>58900</v>
+        <v>93000</v>
       </c>
       <c r="J42" s="3">
+        <v>55700</v>
+      </c>
+      <c r="K42" s="3">
         <v>84800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>70400</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>10</v>
@@ -3571,8 +3660,8 @@
       <c r="P42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3622,417 +3711,432 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4700300</v>
+        <v>5230900</v>
       </c>
       <c r="E43" s="3">
-        <v>4314300</v>
+        <v>4449300</v>
       </c>
       <c r="F43" s="3">
-        <v>4212900</v>
+        <v>4083900</v>
       </c>
       <c r="G43" s="3">
-        <v>4248700</v>
+        <v>3987900</v>
       </c>
       <c r="H43" s="3">
-        <v>4183300</v>
+        <v>4021800</v>
       </c>
       <c r="I43" s="3">
-        <v>3772900</v>
+        <v>3959900</v>
       </c>
       <c r="J43" s="3">
+        <v>3571300</v>
+      </c>
+      <c r="K43" s="3">
         <v>3538700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6216000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3048600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2986800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3239000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3474100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3362100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3641000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4139300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4957300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4749700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4250400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4073400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5283800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4529800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5236600</v>
+        <v>4531100</v>
       </c>
       <c r="E44" s="3">
-        <v>5077600</v>
+        <v>4956900</v>
       </c>
       <c r="F44" s="3">
-        <v>4847300</v>
+        <v>4806400</v>
       </c>
       <c r="G44" s="3">
-        <v>4653500</v>
+        <v>4588400</v>
       </c>
       <c r="H44" s="3">
-        <v>4916700</v>
+        <v>4404900</v>
       </c>
       <c r="I44" s="3">
-        <v>4734200</v>
+        <v>4654100</v>
       </c>
       <c r="J44" s="3">
+        <v>4481400</v>
+      </c>
+      <c r="K44" s="3">
         <v>4455300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8460400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4786300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4723100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4566000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4669100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5015600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5136400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5615900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5564900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6074600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5759800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5787500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5697000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6032500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5635200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>812100</v>
+        <v>648500</v>
       </c>
       <c r="E45" s="3">
-        <v>770000</v>
+        <v>768700</v>
       </c>
       <c r="F45" s="3">
-        <v>823500</v>
+        <v>728900</v>
       </c>
       <c r="G45" s="3">
-        <v>676600</v>
+        <v>779600</v>
       </c>
       <c r="H45" s="3">
-        <v>791000</v>
+        <v>640500</v>
       </c>
       <c r="I45" s="3">
-        <v>713800</v>
+        <v>748700</v>
       </c>
       <c r="J45" s="3">
+        <v>675700</v>
+      </c>
+      <c r="K45" s="3">
         <v>706900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1156000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>815400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>741800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>571100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>307100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>499700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>442900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>528600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>450900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>604200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>561800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>592100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>435700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>816100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>761300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>773600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>655800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>847500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>969300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11529200</v>
+        <v>11017800</v>
       </c>
       <c r="E46" s="3">
-        <v>10809700</v>
+        <v>10913400</v>
       </c>
       <c r="F46" s="3">
-        <v>10565500</v>
+        <v>10232300</v>
       </c>
       <c r="G46" s="3">
-        <v>10584200</v>
+        <v>10001200</v>
       </c>
       <c r="H46" s="3">
-        <v>10582400</v>
+        <v>10018800</v>
       </c>
       <c r="I46" s="3">
-        <v>9839500</v>
+        <v>10017200</v>
       </c>
       <c r="J46" s="3">
+        <v>9314000</v>
+      </c>
+      <c r="K46" s="3">
         <v>9314700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8766200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9167300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8802400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9020900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9113500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9995900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10134700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11250000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11089900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12314000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11454800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11037000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10920200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12605900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11459600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1134900</v>
+        <v>1095500</v>
       </c>
       <c r="E47" s="3">
-        <v>1141000</v>
+        <v>1074300</v>
       </c>
       <c r="F47" s="3">
-        <v>1094600</v>
+        <v>1080100</v>
       </c>
       <c r="G47" s="3">
-        <v>995300</v>
+        <v>1036100</v>
       </c>
       <c r="H47" s="3">
-        <v>1007600</v>
+        <v>942100</v>
       </c>
       <c r="I47" s="3">
-        <v>1012200</v>
+        <v>953800</v>
       </c>
       <c r="J47" s="3">
+        <v>958100</v>
+      </c>
+      <c r="K47" s="3">
         <v>999500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>928400</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>10</v>
@@ -4097,198 +4201,207 @@
       <c r="AG47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3694600</v>
+        <v>3580200</v>
       </c>
       <c r="E48" s="3">
-        <v>3643700</v>
+        <v>3497300</v>
       </c>
       <c r="F48" s="3">
-        <v>3566000</v>
+        <v>3449100</v>
       </c>
       <c r="G48" s="3">
-        <v>3501000</v>
+        <v>3375600</v>
       </c>
       <c r="H48" s="3">
-        <v>3422500</v>
+        <v>3314000</v>
       </c>
       <c r="I48" s="3">
-        <v>3440100</v>
+        <v>3239700</v>
       </c>
       <c r="J48" s="3">
+        <v>3256300</v>
+      </c>
+      <c r="K48" s="3">
         <v>3416200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6289100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3037000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3209100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3284500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3199400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3395700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3631100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4025000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4251400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4416300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4465200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4457200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4667300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4563000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4490400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>459200</v>
+        <v>444200</v>
       </c>
       <c r="E49" s="3">
-        <v>459100</v>
+        <v>434600</v>
       </c>
       <c r="F49" s="3">
-        <v>462900</v>
+        <v>434500</v>
       </c>
       <c r="G49" s="3">
-        <v>446500</v>
+        <v>438200</v>
       </c>
       <c r="H49" s="3">
-        <v>419900</v>
+        <v>422700</v>
       </c>
       <c r="I49" s="3">
-        <v>417800</v>
+        <v>397400</v>
       </c>
       <c r="J49" s="3">
+        <v>395500</v>
+      </c>
+      <c r="K49" s="3">
         <v>415200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>411300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>151800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>159400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>162400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>159000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>161900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>173300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>187600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>188200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>172900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>172200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>163500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>161400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>153300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>149800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>147200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>146200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>139900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>140700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>135000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>135600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>129900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4382,8 +4495,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4477,103 +4593,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1132100</v>
+        <v>961900</v>
       </c>
       <c r="E52" s="3">
-        <v>1177100</v>
+        <v>1071700</v>
       </c>
       <c r="F52" s="3">
-        <v>1031300</v>
+        <v>1114200</v>
       </c>
       <c r="G52" s="3">
-        <v>1038200</v>
+        <v>976300</v>
       </c>
       <c r="H52" s="3">
-        <v>989300</v>
+        <v>982700</v>
       </c>
       <c r="I52" s="3">
-        <v>1007000</v>
+        <v>936400</v>
       </c>
       <c r="J52" s="3">
+        <v>953200</v>
+      </c>
+      <c r="K52" s="3">
         <v>998300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2702900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1706800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1826200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1903300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1457600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1421800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1488900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1726200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1735300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1816600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1839200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1865000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1936100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1603200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1588900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4667,103 +4789,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>17950000</v>
+        <v>17099500</v>
       </c>
       <c r="E54" s="3">
-        <v>17230700</v>
+        <v>16991300</v>
       </c>
       <c r="F54" s="3">
-        <v>16720400</v>
+        <v>16310300</v>
       </c>
       <c r="G54" s="3">
-        <v>16565100</v>
+        <v>15827300</v>
       </c>
       <c r="H54" s="3">
-        <v>16421600</v>
+        <v>15680300</v>
       </c>
       <c r="I54" s="3">
-        <v>15716500</v>
+        <v>15544500</v>
       </c>
       <c r="J54" s="3">
+        <v>14877100</v>
+      </c>
+      <c r="K54" s="3">
         <v>15143900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14439500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14053900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13987200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14360900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13919600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14965300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15415400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17173200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17248600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18707700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17918500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17509700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17671400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18892700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17656100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4797,8 +4925,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4832,578 +4961,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3211600</v>
+        <v>3328700</v>
       </c>
       <c r="E57" s="3">
-        <v>3076200</v>
+        <v>3040000</v>
       </c>
       <c r="F57" s="3">
-        <v>2944200</v>
+        <v>2911900</v>
       </c>
       <c r="G57" s="3">
-        <v>3048200</v>
+        <v>2786900</v>
       </c>
       <c r="H57" s="3">
-        <v>2919300</v>
+        <v>2885400</v>
       </c>
       <c r="I57" s="3">
-        <v>2681800</v>
+        <v>2763400</v>
       </c>
       <c r="J57" s="3">
+        <v>2538500</v>
+      </c>
+      <c r="K57" s="3">
         <v>2548400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4941500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2174500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2173700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2313900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2518000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2447800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2367500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2621900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3274500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3083100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2942400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3095300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3558300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3258700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3116400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3855600</v>
+        <v>2894600</v>
       </c>
       <c r="E58" s="3">
-        <v>3172600</v>
+        <v>3649600</v>
       </c>
       <c r="F58" s="3">
-        <v>2761900</v>
+        <v>3003200</v>
       </c>
       <c r="G58" s="3">
-        <v>2172000</v>
+        <v>2614400</v>
       </c>
       <c r="H58" s="3">
-        <v>2782000</v>
+        <v>2056000</v>
       </c>
       <c r="I58" s="3">
-        <v>2448000</v>
+        <v>2633400</v>
       </c>
       <c r="J58" s="3">
+        <v>2317200</v>
+      </c>
+      <c r="K58" s="3">
         <v>2187200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3378000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1223400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1279500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1016400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1224000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1345800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1415400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1634900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1653900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2582000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1721200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1287200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1060400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2197400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1264300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>976200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3459800</v>
+        <v>3611500</v>
       </c>
       <c r="E59" s="3">
-        <v>3730200</v>
+        <v>3275000</v>
       </c>
       <c r="F59" s="3">
-        <v>3369200</v>
+        <v>3531000</v>
       </c>
       <c r="G59" s="3">
-        <v>3600200</v>
+        <v>3189300</v>
       </c>
       <c r="H59" s="3">
-        <v>3075000</v>
+        <v>3407900</v>
       </c>
       <c r="I59" s="3">
-        <v>3048000</v>
+        <v>2910700</v>
       </c>
       <c r="J59" s="3">
+        <v>2885200</v>
+      </c>
+      <c r="K59" s="3">
         <v>3042600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4901600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3758300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3306200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3568900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2763500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3549100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3645000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3728900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3421000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4249500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4400600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4389200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3687000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4536000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4683500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10526900</v>
+        <v>9834700</v>
       </c>
       <c r="E60" s="3">
-        <v>9979100</v>
+        <v>9964600</v>
       </c>
       <c r="F60" s="3">
-        <v>9075300</v>
+        <v>9446100</v>
       </c>
       <c r="G60" s="3">
-        <v>8820400</v>
+        <v>8590600</v>
       </c>
       <c r="H60" s="3">
-        <v>8776300</v>
+        <v>8349300</v>
       </c>
       <c r="I60" s="3">
-        <v>8177700</v>
+        <v>8307500</v>
       </c>
       <c r="J60" s="3">
+        <v>7741000</v>
+      </c>
+      <c r="K60" s="3">
         <v>7778200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7036600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7156200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6759400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6899100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6505500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7342700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7428000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7985700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8349500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9914600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9064200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8771700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8305700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9992100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9064200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2691700</v>
+        <v>2498000</v>
       </c>
       <c r="E61" s="3">
-        <v>2573800</v>
+        <v>2547900</v>
       </c>
       <c r="F61" s="3">
-        <v>2815200</v>
+        <v>2436300</v>
       </c>
       <c r="G61" s="3">
-        <v>2950500</v>
+        <v>2664800</v>
       </c>
       <c r="H61" s="3">
-        <v>2899500</v>
+        <v>2792900</v>
       </c>
       <c r="I61" s="3">
-        <v>2916400</v>
+        <v>2744700</v>
       </c>
       <c r="J61" s="3">
+        <v>2760600</v>
+      </c>
+      <c r="K61" s="3">
         <v>2896400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2978600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2553900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2705600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2831300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2826800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2831300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3012800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3572900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3081100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3024000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3087500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2996100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3162500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2995400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2840900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>759400</v>
+        <v>590800</v>
       </c>
       <c r="E62" s="3">
-        <v>756800</v>
+        <v>718900</v>
       </c>
       <c r="F62" s="3">
-        <v>750500</v>
+        <v>716400</v>
       </c>
       <c r="G62" s="3">
-        <v>771300</v>
+        <v>710500</v>
       </c>
       <c r="H62" s="3">
-        <v>854800</v>
+        <v>730100</v>
       </c>
       <c r="I62" s="3">
-        <v>855100</v>
+        <v>809200</v>
       </c>
       <c r="J62" s="3">
+        <v>809400</v>
+      </c>
+      <c r="K62" s="3">
         <v>844300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1233200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1200600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1262100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1277500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1164400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1444200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1537400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1711600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1663500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1441800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1418300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1393600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1472600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1362100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1360700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5497,8 +5645,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5592,8 +5743,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5687,103 +5841,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14116400</v>
+        <v>13054000</v>
       </c>
       <c r="E66" s="3">
-        <v>13443900</v>
+        <v>13362500</v>
       </c>
       <c r="F66" s="3">
-        <v>12779100</v>
+        <v>12725900</v>
       </c>
       <c r="G66" s="3">
-        <v>12681500</v>
+        <v>12096500</v>
       </c>
       <c r="H66" s="3">
-        <v>12654600</v>
+        <v>12004100</v>
       </c>
       <c r="I66" s="3">
-        <v>12074000</v>
+        <v>11978700</v>
       </c>
       <c r="J66" s="3">
+        <v>11429100</v>
+      </c>
+      <c r="K66" s="3">
         <v>11640400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11083100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11040200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10858200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11138400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10620400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11739800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12100800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13401500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13234500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14525700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13713800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13304000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13093300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14506700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13411300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5817,8 +5977,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5912,8 +6073,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6007,8 +6171,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6102,8 +6269,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6197,103 +6367,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2380000</v>
+        <v>2584900</v>
       </c>
       <c r="E72" s="3">
-        <v>2337500</v>
+        <v>2252900</v>
       </c>
       <c r="F72" s="3">
-        <v>2556600</v>
+        <v>2212700</v>
       </c>
       <c r="G72" s="3">
-        <v>2562900</v>
+        <v>2420000</v>
       </c>
       <c r="H72" s="3">
-        <v>2462100</v>
+        <v>2426000</v>
       </c>
       <c r="I72" s="3">
-        <v>2303400</v>
+        <v>2330600</v>
       </c>
       <c r="J72" s="3">
+        <v>2180400</v>
+      </c>
+      <c r="K72" s="3">
         <v>2178900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2129300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1860900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1957200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2034500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2173600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2286100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2332000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2685700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2877600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2848900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2849600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2798900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3119500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2912600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2781500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6387,8 +6563,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6482,8 +6661,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6577,103 +6759,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3833600</v>
+        <v>4045500</v>
       </c>
       <c r="E76" s="3">
-        <v>3786700</v>
+        <v>3628800</v>
       </c>
       <c r="F76" s="3">
-        <v>3941300</v>
+        <v>3584500</v>
       </c>
       <c r="G76" s="3">
-        <v>3883600</v>
+        <v>3730800</v>
       </c>
       <c r="H76" s="3">
-        <v>3767000</v>
+        <v>3676200</v>
       </c>
       <c r="I76" s="3">
-        <v>3642500</v>
+        <v>3565800</v>
       </c>
       <c r="J76" s="3">
+        <v>3448000</v>
+      </c>
+      <c r="K76" s="3">
         <v>3503500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3356400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3013700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3128900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3222500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3299200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3225400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3314600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3771700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4014100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4182100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4204800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4205800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4578100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4386000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4244700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6767,203 +6955,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>66500</v>
+        <v>247900</v>
       </c>
       <c r="E81" s="3">
-        <v>-218600</v>
+        <v>62900</v>
       </c>
       <c r="F81" s="3">
-        <v>61300</v>
+        <v>-206900</v>
       </c>
       <c r="G81" s="3">
-        <v>3500</v>
+        <v>58000</v>
       </c>
       <c r="H81" s="3">
-        <v>193800</v>
+        <v>3300</v>
       </c>
       <c r="I81" s="3">
-        <v>123400</v>
+        <v>183400</v>
       </c>
       <c r="J81" s="3">
+        <v>116800</v>
+      </c>
+      <c r="K81" s="3">
         <v>36800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>80700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>97500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-120700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>122500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>77400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-75600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>154400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>141400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-57200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>130100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>68500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>29600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>73000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>161600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6997,103 +7194,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>117900</v>
+        <v>127400</v>
       </c>
       <c r="E83" s="3">
-        <v>149200</v>
+        <v>111600</v>
       </c>
       <c r="F83" s="3">
-        <v>144200</v>
+        <v>141200</v>
       </c>
       <c r="G83" s="3">
-        <v>144200</v>
+        <v>136500</v>
       </c>
       <c r="H83" s="3">
-        <v>124000</v>
+        <v>136500</v>
       </c>
       <c r="I83" s="3">
-        <v>125200</v>
+        <v>117400</v>
       </c>
       <c r="J83" s="3">
+        <v>118500</v>
+      </c>
+      <c r="K83" s="3">
         <v>128100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>133000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>139400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>137300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>112000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>111700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>118200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>128300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>139600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>139400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>141400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>135100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>143800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>139000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>136000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>133600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>130900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>128500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>125300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>122800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>119500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>115100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7187,8 +7388,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7282,8 +7486,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7377,8 +7584,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7472,8 +7682,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7567,52 +7780,55 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-555900</v>
+        <v>826700</v>
       </c>
       <c r="E89" s="3">
-        <v>47100</v>
+        <v>-526200</v>
       </c>
       <c r="F89" s="3">
-        <v>-151200</v>
+        <v>44600</v>
       </c>
       <c r="G89" s="3">
-        <v>921600</v>
+        <v>-143100</v>
       </c>
       <c r="H89" s="3">
-        <v>-290400</v>
+        <v>872400</v>
       </c>
       <c r="I89" s="3">
-        <v>-54200</v>
+        <v>-274900</v>
       </c>
       <c r="J89" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-417800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1942400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-353600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-393600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-217400</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -7662,8 +7878,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7697,52 +7916,53 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15981000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32106000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29437000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19019000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31195000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-103000</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7792,8 +8012,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7887,8 +8110,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7982,52 +8208,55 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-222500</v>
+        <v>-55500</v>
       </c>
       <c r="E94" s="3">
-        <v>-175900</v>
+        <v>-210600</v>
       </c>
       <c r="F94" s="3">
-        <v>-148200</v>
+        <v>-166500</v>
       </c>
       <c r="G94" s="3">
-        <v>-163000</v>
+        <v>-140300</v>
       </c>
       <c r="H94" s="3">
-        <v>-120100</v>
+        <v>-154300</v>
       </c>
       <c r="I94" s="3">
-        <v>-76900</v>
+        <v>-113700</v>
       </c>
       <c r="J94" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-162000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-125500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-105300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-99800</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -8077,8 +8306,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8112,47 +8344,48 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M96" s="3">
         <v>-21300</v>
       </c>
-      <c r="E96" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-62900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-31200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-20800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -8207,8 +8440,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8302,8 +8538,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8397,8 +8636,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8492,52 +8734,55 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>870400</v>
+        <v>-853900</v>
       </c>
       <c r="E100" s="3">
-        <v>105700</v>
+        <v>823900</v>
       </c>
       <c r="F100" s="3">
-        <v>13000</v>
+        <v>100000</v>
       </c>
       <c r="G100" s="3">
-        <v>-446600</v>
+        <v>12300</v>
       </c>
       <c r="H100" s="3">
-        <v>406700</v>
+        <v>-422700</v>
       </c>
       <c r="I100" s="3">
-        <v>191700</v>
+        <v>385000</v>
       </c>
       <c r="J100" s="3">
+        <v>181500</v>
+      </c>
+      <c r="K100" s="3">
         <v>423100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>510300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>128200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>277100</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -8587,52 +8832,55 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>19900</v>
+        <v>-31300</v>
       </c>
       <c r="E101" s="3">
-        <v>-20400</v>
+        <v>18800</v>
       </c>
       <c r="F101" s="3">
-        <v>-27200</v>
+        <v>-19400</v>
       </c>
       <c r="G101" s="3">
-        <v>27900</v>
+        <v>-25800</v>
       </c>
       <c r="H101" s="3">
-        <v>37100</v>
+        <v>26400</v>
       </c>
       <c r="I101" s="3">
-        <v>-30000</v>
+        <v>35100</v>
       </c>
       <c r="J101" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-45500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2600</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8682,52 +8930,55 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>111900</v>
+        <v>-114000</v>
       </c>
       <c r="E102" s="3">
-        <v>-43600</v>
+        <v>105900</v>
       </c>
       <c r="F102" s="3">
-        <v>-313700</v>
+        <v>-41200</v>
       </c>
       <c r="G102" s="3">
-        <v>339800</v>
+        <v>-296900</v>
       </c>
       <c r="H102" s="3">
-        <v>33400</v>
+        <v>321700</v>
       </c>
       <c r="I102" s="3">
-        <v>30700</v>
+        <v>31600</v>
       </c>
       <c r="J102" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-202300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>264600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>95400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-449100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-37500</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -8775,6 +9026,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,434 +656,446 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3957000</v>
+        <v>3154000</v>
       </c>
       <c r="E8" s="3">
-        <v>2933100</v>
+        <v>4403500</v>
       </c>
       <c r="F8" s="3">
-        <v>2322300</v>
+        <v>3264100</v>
       </c>
       <c r="G8" s="3">
-        <v>2586100</v>
+        <v>2584400</v>
       </c>
       <c r="H8" s="3">
-        <v>3376800</v>
+        <v>2877900</v>
       </c>
       <c r="I8" s="3">
-        <v>2785400</v>
+        <v>3757900</v>
       </c>
       <c r="J8" s="3">
+        <v>3099700</v>
+      </c>
+      <c r="K8" s="3">
         <v>2612000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2361300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3069000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2457000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2346600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2613400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3233100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2749900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2778900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2564100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4456900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3633800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3545400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3213100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4806500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3837100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3198800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3182000</v>
+        <v>2547500</v>
       </c>
       <c r="E9" s="3">
-        <v>2280000</v>
+        <v>3541100</v>
       </c>
       <c r="F9" s="3">
-        <v>2179900</v>
+        <v>2537300</v>
       </c>
       <c r="G9" s="3">
-        <v>2164400</v>
+        <v>2425900</v>
       </c>
       <c r="H9" s="3">
-        <v>2821800</v>
+        <v>2408700</v>
       </c>
       <c r="I9" s="3">
-        <v>2104400</v>
+        <v>3140200</v>
       </c>
       <c r="J9" s="3">
+        <v>2341900</v>
+      </c>
+      <c r="K9" s="3">
         <v>2084200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1974600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2645300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1965700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1960400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2140300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2819800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2277000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2419600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2374400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3671300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2955100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3016900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2761100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4003100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3097700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2730600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>775000</v>
+        <v>606500</v>
       </c>
       <c r="E10" s="3">
-        <v>653000</v>
+        <v>862400</v>
       </c>
       <c r="F10" s="3">
-        <v>142400</v>
+        <v>726700</v>
       </c>
       <c r="G10" s="3">
-        <v>421700</v>
+        <v>158500</v>
       </c>
       <c r="H10" s="3">
-        <v>555000</v>
+        <v>469300</v>
       </c>
       <c r="I10" s="3">
-        <v>681000</v>
+        <v>617700</v>
       </c>
       <c r="J10" s="3">
+        <v>757800</v>
+      </c>
+      <c r="K10" s="3">
         <v>527700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>386700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>423600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>491400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>386200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>473100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>413200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>472900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>359300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>189700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>785600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>678700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>528500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>452100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>803400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>739500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>468200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>506600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>600700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>704100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>533500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>462600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>662000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>561100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1118,8 +1130,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1147,77 +1160,80 @@
       <c r="K12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3">
         <v>101800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>82100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>78900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>65300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>107800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>78500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>84900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>69500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>143000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>115100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>116000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>101800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>147100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>115000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>101400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>93800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>129900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>94100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>101300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>85500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>113200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>90400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1314,8 +1330,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,38 +1362,38 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>9100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>110500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>30500</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>21700</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
@@ -1391,14 +1410,14 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>116000</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1412,8 +1431,11 @@
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1510,8 +1532,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1543,204 +1568,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3667000</v>
+        <v>3033800</v>
       </c>
       <c r="E17" s="3">
-        <v>2718800</v>
+        <v>4080800</v>
       </c>
       <c r="F17" s="3">
-        <v>2597300</v>
+        <v>3025600</v>
       </c>
       <c r="G17" s="3">
-        <v>2520700</v>
+        <v>2890400</v>
       </c>
       <c r="H17" s="3">
-        <v>3367400</v>
+        <v>2805100</v>
       </c>
       <c r="I17" s="3">
-        <v>2466100</v>
+        <v>3747400</v>
       </c>
       <c r="J17" s="3">
+        <v>2744400</v>
+      </c>
+      <c r="K17" s="3">
         <v>2444600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2330400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3058200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2380700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2353200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2477100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3354700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2617100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2818900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2740400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4183100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3452300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3475600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3203200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4545400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3569100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3186200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>290000</v>
+        <v>120200</v>
       </c>
       <c r="E18" s="3">
-        <v>214300</v>
+        <v>322800</v>
       </c>
       <c r="F18" s="3">
-        <v>-275000</v>
+        <v>238500</v>
       </c>
       <c r="G18" s="3">
-        <v>65400</v>
+        <v>-306000</v>
       </c>
       <c r="H18" s="3">
-        <v>9400</v>
+        <v>72800</v>
       </c>
       <c r="I18" s="3">
-        <v>319300</v>
+        <v>10400</v>
       </c>
       <c r="J18" s="3">
+        <v>355400</v>
+      </c>
+      <c r="K18" s="3">
         <v>167400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>76300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>136300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-121600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>132800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-176200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>273800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>181500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>69800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>261100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>268000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>64600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>102000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>141900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>101300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>44400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>204800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>127600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1775,204 +1807,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>28400</v>
+        <v>63500</v>
       </c>
       <c r="E20" s="3">
-        <v>-108800</v>
+        <v>31600</v>
       </c>
       <c r="F20" s="3">
-        <v>-40400</v>
+        <v>-121000</v>
       </c>
       <c r="G20" s="3">
-        <v>30100</v>
+        <v>-45000</v>
       </c>
       <c r="H20" s="3">
-        <v>-20700</v>
+        <v>33500</v>
       </c>
       <c r="I20" s="3">
-        <v>-88500</v>
+        <v>-23100</v>
       </c>
       <c r="J20" s="3">
+        <v>-98500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>40500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>21700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>64600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-45800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-62200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-41800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-79300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-73400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>20000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>98500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>445800</v>
+        <v>332000</v>
       </c>
       <c r="E21" s="3">
-        <v>217100</v>
+        <v>496100</v>
       </c>
       <c r="F21" s="3">
-        <v>-174200</v>
+        <v>241600</v>
       </c>
       <c r="G21" s="3">
-        <v>232000</v>
+        <v>-193900</v>
       </c>
       <c r="H21" s="3">
-        <v>125200</v>
+        <v>258100</v>
       </c>
       <c r="I21" s="3">
-        <v>348200</v>
+        <v>139300</v>
       </c>
       <c r="J21" s="3">
+        <v>387500</v>
+      </c>
+      <c r="K21" s="3">
         <v>280200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>199600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>157900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>204500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>128900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>269200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>252100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>100000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>367600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>258700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>209800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>103200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>325600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>333600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>65900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>218200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>190700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>243500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>218900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>177900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>246600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>341100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2000,273 +2039,282 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
         <v>5600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>6100</v>
       </c>
       <c r="AD22" s="3">
         <v>6100</v>
       </c>
       <c r="AE22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AF22" s="3">
         <v>6000</v>
       </c>
       <c r="AG22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>6700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>318400</v>
+        <v>183800</v>
       </c>
       <c r="E23" s="3">
-        <v>105500</v>
+        <v>354400</v>
       </c>
       <c r="F23" s="3">
-        <v>-315400</v>
+        <v>117400</v>
       </c>
       <c r="G23" s="3">
-        <v>95500</v>
+        <v>-351000</v>
       </c>
       <c r="H23" s="3">
-        <v>-11300</v>
+        <v>106300</v>
       </c>
       <c r="I23" s="3">
-        <v>230800</v>
+        <v>-12600</v>
       </c>
       <c r="J23" s="3">
+        <v>256900</v>
+      </c>
+      <c r="K23" s="3">
         <v>161700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>71500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>68700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>125400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-109900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>133400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-120400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>220700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>110800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>59700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-40200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>172900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>185600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-77500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>77700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>52700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>108900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>87500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>49100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>121200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>219400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>76400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>42400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-124800</v>
+      </c>
+      <c r="H24" s="3">
+        <v>39200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>48900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>42800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>32400</v>
+      </c>
+      <c r="M24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="N24" s="3">
+        <v>36100</v>
+      </c>
+      <c r="O24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P24" s="3">
+        <v>37900</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-76400</v>
+      </c>
+      <c r="R24" s="3">
+        <v>30200</v>
+      </c>
+      <c r="S24" s="3">
+        <v>92100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="U24" s="3">
+        <v>93700</v>
+      </c>
+      <c r="V24" s="3">
+        <v>30000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>14200</v>
+      </c>
+      <c r="X24" s="3">
+        <v>32800</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>35700</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>-83100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>68700</v>
       </c>
-      <c r="E24" s="3">
-        <v>38100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-112200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>35200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>43900</v>
-      </c>
-      <c r="J24" s="3">
-        <v>42800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>32400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>6900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>36100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>9900</v>
-      </c>
-      <c r="O24" s="3">
-        <v>37900</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-76400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>30200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>92100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-20200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>93700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>30000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>14200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>32800</v>
-      </c>
-      <c r="X24" s="3">
-        <v>12500</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>35700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>51200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-83100</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>68700</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2363,204 +2411,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>249800</v>
+        <v>113200</v>
       </c>
       <c r="E26" s="3">
-        <v>67500</v>
+        <v>277900</v>
       </c>
       <c r="F26" s="3">
-        <v>-203300</v>
+        <v>75100</v>
       </c>
       <c r="G26" s="3">
-        <v>60300</v>
+        <v>-226200</v>
       </c>
       <c r="H26" s="3">
-        <v>10000</v>
+        <v>67100</v>
       </c>
       <c r="I26" s="3">
-        <v>186900</v>
+        <v>11100</v>
       </c>
       <c r="J26" s="3">
+        <v>208000</v>
+      </c>
+      <c r="K26" s="3">
         <v>118900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>39100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>87500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>103100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-117600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>127000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>80800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>45500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-73000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>160400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>149900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>135900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>40200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>74000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>78000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>165300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>247900</v>
+        <v>109200</v>
       </c>
       <c r="E27" s="3">
-        <v>62900</v>
+        <v>275900</v>
       </c>
       <c r="F27" s="3">
-        <v>-206900</v>
+        <v>70000</v>
       </c>
       <c r="G27" s="3">
-        <v>58000</v>
+        <v>-230300</v>
       </c>
       <c r="H27" s="3">
-        <v>3300</v>
+        <v>64500</v>
       </c>
       <c r="I27" s="3">
-        <v>183400</v>
+        <v>3700</v>
       </c>
       <c r="J27" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K27" s="3">
         <v>116800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>80700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>97500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-120700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>122500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>77400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>41500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-75600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>154400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>141400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>23300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>130100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>68500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>29600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>73000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>161600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2657,8 +2714,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2755,8 +2815,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2853,8 +2916,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2951,204 +3017,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-28400</v>
+        <v>-63500</v>
       </c>
       <c r="E32" s="3">
-        <v>108800</v>
+        <v>-31600</v>
       </c>
       <c r="F32" s="3">
-        <v>40400</v>
+        <v>121000</v>
       </c>
       <c r="G32" s="3">
-        <v>-30100</v>
+        <v>45000</v>
       </c>
       <c r="H32" s="3">
-        <v>20700</v>
+        <v>-33500</v>
       </c>
       <c r="I32" s="3">
-        <v>88500</v>
+        <v>23100</v>
       </c>
       <c r="J32" s="3">
+        <v>98500</v>
+      </c>
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-40500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-21700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-64600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>45800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>62200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>41800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>79300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>73400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>82700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>42200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>26800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>77600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>247900</v>
+        <v>109200</v>
       </c>
       <c r="E33" s="3">
-        <v>62900</v>
+        <v>275900</v>
       </c>
       <c r="F33" s="3">
-        <v>-206900</v>
+        <v>70000</v>
       </c>
       <c r="G33" s="3">
-        <v>58000</v>
+        <v>-230300</v>
       </c>
       <c r="H33" s="3">
-        <v>3300</v>
+        <v>64500</v>
       </c>
       <c r="I33" s="3">
-        <v>183400</v>
+        <v>3700</v>
       </c>
       <c r="J33" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K33" s="3">
         <v>116800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>80700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>97500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-120700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>122500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>77400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-75600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>154400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>141400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>130100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>68500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>29600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>73000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>161600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3245,209 +3320,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>247900</v>
+        <v>109200</v>
       </c>
       <c r="E35" s="3">
-        <v>62900</v>
+        <v>275900</v>
       </c>
       <c r="F35" s="3">
-        <v>-206900</v>
+        <v>70000</v>
       </c>
       <c r="G35" s="3">
-        <v>58000</v>
+        <v>-230300</v>
       </c>
       <c r="H35" s="3">
-        <v>3300</v>
+        <v>64500</v>
       </c>
       <c r="I35" s="3">
-        <v>183400</v>
+        <v>3700</v>
       </c>
       <c r="J35" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K35" s="3">
         <v>116800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>80700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>97500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-120700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>122500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>77400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-75600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>154400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>141400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>130100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>68500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>29600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>73000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>161600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3482,8 +3566,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3518,138 +3603,142 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>536900</v>
+        <v>730300</v>
       </c>
       <c r="E41" s="3">
-        <v>650900</v>
+        <v>597500</v>
       </c>
       <c r="F41" s="3">
-        <v>544900</v>
+        <v>724300</v>
       </c>
       <c r="G41" s="3">
-        <v>586200</v>
+        <v>606400</v>
       </c>
       <c r="H41" s="3">
-        <v>883100</v>
+        <v>652300</v>
       </c>
       <c r="I41" s="3">
-        <v>561400</v>
+        <v>982800</v>
       </c>
       <c r="J41" s="3">
+        <v>624800</v>
+      </c>
+      <c r="K41" s="3">
         <v>529800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>529100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1480600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>517000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>436900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>897100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>898300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1006600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1193300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1464500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>934800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>677900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>383600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>407000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>714100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>473500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>533400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>527700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>638500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>455700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>410800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>436300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>491300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>474100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>70300</v>
+        <v>104200</v>
       </c>
       <c r="E42" s="3">
-        <v>87700</v>
+        <v>78300</v>
       </c>
       <c r="F42" s="3">
-        <v>68300</v>
+        <v>97600</v>
       </c>
       <c r="G42" s="3">
-        <v>59200</v>
+        <v>76000</v>
       </c>
       <c r="H42" s="3">
-        <v>68500</v>
+        <v>65900</v>
       </c>
       <c r="I42" s="3">
-        <v>93000</v>
+        <v>76300</v>
       </c>
       <c r="J42" s="3">
+        <v>103500</v>
+      </c>
+      <c r="K42" s="3">
         <v>55700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>84800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>70400</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>10</v>
@@ -3663,8 +3752,8 @@
       <c r="Q42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3714,432 +3803,447 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5230900</v>
+        <v>5552200</v>
       </c>
       <c r="E43" s="3">
-        <v>4449300</v>
+        <v>5821200</v>
       </c>
       <c r="F43" s="3">
-        <v>4083900</v>
+        <v>4951400</v>
       </c>
       <c r="G43" s="3">
-        <v>3987900</v>
+        <v>4544800</v>
       </c>
       <c r="H43" s="3">
-        <v>4021800</v>
+        <v>4437900</v>
       </c>
       <c r="I43" s="3">
-        <v>3959900</v>
+        <v>4475600</v>
       </c>
       <c r="J43" s="3">
+        <v>4406800</v>
+      </c>
+      <c r="K43" s="3">
         <v>3571300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3538700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6216000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3048600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2900600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2986800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3239000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3474100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3362100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3641000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4139300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4957300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4749700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4250400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4073400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5283800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4529800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4531100</v>
+        <v>5504800</v>
       </c>
       <c r="E44" s="3">
-        <v>4956900</v>
+        <v>5042500</v>
       </c>
       <c r="F44" s="3">
-        <v>4806400</v>
+        <v>5516300</v>
       </c>
       <c r="G44" s="3">
-        <v>4588400</v>
+        <v>5348800</v>
       </c>
       <c r="H44" s="3">
-        <v>4404900</v>
+        <v>5106200</v>
       </c>
       <c r="I44" s="3">
-        <v>4654100</v>
+        <v>4902100</v>
       </c>
       <c r="J44" s="3">
+        <v>5179300</v>
+      </c>
+      <c r="K44" s="3">
         <v>4481400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4455300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8460400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4786300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4723100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4566000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4669100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5015600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5136400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5615900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5564900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6074600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5759800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5787500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5697000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6032500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5635200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>648500</v>
+        <v>1087400</v>
       </c>
       <c r="E45" s="3">
-        <v>768700</v>
+        <v>721700</v>
       </c>
       <c r="F45" s="3">
-        <v>728900</v>
+        <v>855400</v>
       </c>
       <c r="G45" s="3">
-        <v>779600</v>
+        <v>811100</v>
       </c>
       <c r="H45" s="3">
-        <v>640500</v>
+        <v>867500</v>
       </c>
       <c r="I45" s="3">
-        <v>748700</v>
+        <v>712700</v>
       </c>
       <c r="J45" s="3">
+        <v>833200</v>
+      </c>
+      <c r="K45" s="3">
         <v>675700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>706900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1156000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>815400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>741800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>571100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>307100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>499700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>442900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>528600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>450900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>604200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>561800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>592100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>435700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>816100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>761300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>773600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>655800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>847500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>969300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11017800</v>
+        <v>12978900</v>
       </c>
       <c r="E46" s="3">
-        <v>10913400</v>
+        <v>12261200</v>
       </c>
       <c r="F46" s="3">
-        <v>10232300</v>
+        <v>12145000</v>
       </c>
       <c r="G46" s="3">
-        <v>10001200</v>
+        <v>11387100</v>
       </c>
       <c r="H46" s="3">
-        <v>10018800</v>
+        <v>11129900</v>
       </c>
       <c r="I46" s="3">
-        <v>10017200</v>
+        <v>11149500</v>
       </c>
       <c r="J46" s="3">
+        <v>11147600</v>
+      </c>
+      <c r="K46" s="3">
         <v>9314000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9314700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8766200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9167300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8802400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9020900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9113500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9995900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10134700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11250000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11089900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12314000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11454800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11037000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10920200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12605900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11459600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1095500</v>
+        <v>1315900</v>
       </c>
       <c r="E47" s="3">
-        <v>1074300</v>
+        <v>1219200</v>
       </c>
       <c r="F47" s="3">
-        <v>1080100</v>
+        <v>1195500</v>
       </c>
       <c r="G47" s="3">
-        <v>1036100</v>
+        <v>1202000</v>
       </c>
       <c r="H47" s="3">
-        <v>942100</v>
+        <v>1153100</v>
       </c>
       <c r="I47" s="3">
-        <v>953800</v>
+        <v>1048400</v>
       </c>
       <c r="J47" s="3">
+        <v>1061400</v>
+      </c>
+      <c r="K47" s="3">
         <v>958100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>999500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>928400</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>10</v>
@@ -4204,204 +4308,213 @@
       <c r="AH47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3580200</v>
+        <v>4122400</v>
       </c>
       <c r="E48" s="3">
-        <v>3497300</v>
+        <v>3984200</v>
       </c>
       <c r="F48" s="3">
-        <v>3449100</v>
+        <v>3892000</v>
       </c>
       <c r="G48" s="3">
-        <v>3375600</v>
+        <v>3838400</v>
       </c>
       <c r="H48" s="3">
-        <v>3314000</v>
+        <v>3756500</v>
       </c>
       <c r="I48" s="3">
-        <v>3239700</v>
+        <v>3688000</v>
       </c>
       <c r="J48" s="3">
+        <v>3605300</v>
+      </c>
+      <c r="K48" s="3">
         <v>3256300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3416200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6289100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3037000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3209100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3284500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3199400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3395700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3631100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4025000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4251400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4416300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4465200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4457200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4667300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4563000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4490400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>444200</v>
+        <v>501200</v>
       </c>
       <c r="E49" s="3">
-        <v>434600</v>
+        <v>494300</v>
       </c>
       <c r="F49" s="3">
-        <v>434500</v>
+        <v>483700</v>
       </c>
       <c r="G49" s="3">
-        <v>438200</v>
+        <v>483600</v>
       </c>
       <c r="H49" s="3">
-        <v>422700</v>
+        <v>487600</v>
       </c>
       <c r="I49" s="3">
-        <v>397400</v>
+        <v>470400</v>
       </c>
       <c r="J49" s="3">
+        <v>442300</v>
+      </c>
+      <c r="K49" s="3">
         <v>395500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>415200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>411300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>151800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>159400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>162400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>159000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>161900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>173300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>187600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>188200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>172900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>172200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>163500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>161400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>153300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>149800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>147200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>146200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>139900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>140700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>135000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>135600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>129900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4498,8 +4611,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4596,106 +4712,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>961900</v>
+        <v>1070800</v>
       </c>
       <c r="E52" s="3">
-        <v>1071700</v>
+        <v>1070400</v>
       </c>
       <c r="F52" s="3">
-        <v>1114200</v>
+        <v>1192600</v>
       </c>
       <c r="G52" s="3">
-        <v>976300</v>
+        <v>1240000</v>
       </c>
       <c r="H52" s="3">
-        <v>982700</v>
+        <v>1086400</v>
       </c>
       <c r="I52" s="3">
-        <v>936400</v>
+        <v>1093600</v>
       </c>
       <c r="J52" s="3">
+        <v>1042100</v>
+      </c>
+      <c r="K52" s="3">
         <v>953200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>998300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2702900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1706800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1826200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1903300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1457600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1421800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1488900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1726200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1735300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1816600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1839200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1865000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1936100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1603200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1588900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4792,106 +4914,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>17099500</v>
+        <v>19989200</v>
       </c>
       <c r="E54" s="3">
-        <v>16991300</v>
+        <v>19029200</v>
       </c>
       <c r="F54" s="3">
-        <v>16310300</v>
+        <v>18908800</v>
       </c>
       <c r="G54" s="3">
-        <v>15827300</v>
+        <v>18151000</v>
       </c>
       <c r="H54" s="3">
-        <v>15680300</v>
+        <v>17613500</v>
       </c>
       <c r="I54" s="3">
-        <v>15544500</v>
+        <v>17449800</v>
       </c>
       <c r="J54" s="3">
+        <v>17298800</v>
+      </c>
+      <c r="K54" s="3">
         <v>14877100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15143900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14439500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14053900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13987200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14360900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13919600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14965300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15415400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17173200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17248600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18707700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17918500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17509700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17671400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18892700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17656100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4926,8 +5054,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4962,596 +5091,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3328700</v>
+        <v>3636900</v>
       </c>
       <c r="E57" s="3">
-        <v>3040000</v>
+        <v>3704300</v>
       </c>
       <c r="F57" s="3">
-        <v>2911900</v>
+        <v>3383100</v>
       </c>
       <c r="G57" s="3">
-        <v>2786900</v>
+        <v>3240500</v>
       </c>
       <c r="H57" s="3">
-        <v>2885400</v>
+        <v>3101400</v>
       </c>
       <c r="I57" s="3">
-        <v>2763400</v>
+        <v>3211000</v>
       </c>
       <c r="J57" s="3">
+        <v>3075300</v>
+      </c>
+      <c r="K57" s="3">
         <v>2538500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2548400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4941500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2174500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2173700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2313900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2518000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2447800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2367500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2621900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3274500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3083100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2942400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3095300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3558300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3258700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3116400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2894600</v>
+        <v>3832200</v>
       </c>
       <c r="E58" s="3">
-        <v>3649600</v>
+        <v>3093600</v>
       </c>
       <c r="F58" s="3">
-        <v>3003200</v>
+        <v>4061500</v>
       </c>
       <c r="G58" s="3">
-        <v>2614400</v>
+        <v>3342100</v>
       </c>
       <c r="H58" s="3">
-        <v>2056000</v>
+        <v>2909400</v>
       </c>
       <c r="I58" s="3">
-        <v>2633400</v>
+        <v>2288000</v>
       </c>
       <c r="J58" s="3">
+        <v>2930600</v>
+      </c>
+      <c r="K58" s="3">
         <v>2317200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2187200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3378000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1223400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1279500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1016400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1224000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1345800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1415400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1634900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1653900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2582000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1721200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1287200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1060400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2197400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1264300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>976200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3611500</v>
+        <v>4479300</v>
       </c>
       <c r="E59" s="3">
-        <v>3275000</v>
+        <v>4146700</v>
       </c>
       <c r="F59" s="3">
-        <v>3531000</v>
+        <v>3644600</v>
       </c>
       <c r="G59" s="3">
-        <v>3189300</v>
+        <v>3929500</v>
       </c>
       <c r="H59" s="3">
-        <v>3407900</v>
+        <v>3549200</v>
       </c>
       <c r="I59" s="3">
-        <v>2910700</v>
+        <v>3792500</v>
       </c>
       <c r="J59" s="3">
+        <v>3239200</v>
+      </c>
+      <c r="K59" s="3">
         <v>2885200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3042600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4901600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3758300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3306200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3568900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2763500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3549100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3645000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3728900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3421000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4249500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4400600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4389200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3687000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4536000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4683500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9834700</v>
+        <v>11948400</v>
       </c>
       <c r="E60" s="3">
-        <v>9964600</v>
+        <v>10944600</v>
       </c>
       <c r="F60" s="3">
-        <v>9446100</v>
+        <v>11089200</v>
       </c>
       <c r="G60" s="3">
-        <v>8590600</v>
+        <v>10512100</v>
       </c>
       <c r="H60" s="3">
-        <v>8349300</v>
+        <v>9560000</v>
       </c>
       <c r="I60" s="3">
-        <v>8307500</v>
+        <v>9291500</v>
       </c>
       <c r="J60" s="3">
+        <v>9245000</v>
+      </c>
+      <c r="K60" s="3">
         <v>7741000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7778200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7036600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7156200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6759400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6899100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6505500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7342700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7428000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7985700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8349500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9914600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9064200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8771700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8305700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9992100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2498000</v>
+        <v>2557400</v>
       </c>
       <c r="E61" s="3">
-        <v>2547900</v>
+        <v>2744000</v>
       </c>
       <c r="F61" s="3">
-        <v>2436300</v>
+        <v>2835500</v>
       </c>
       <c r="G61" s="3">
-        <v>2664800</v>
+        <v>2711300</v>
       </c>
       <c r="H61" s="3">
-        <v>2792900</v>
+        <v>2965600</v>
       </c>
       <c r="I61" s="3">
-        <v>2744700</v>
+        <v>3108100</v>
       </c>
       <c r="J61" s="3">
+        <v>3054400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2760600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2896400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2978600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2553900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2705600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2831300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2826800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2831300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3012800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3572900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3081100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3024000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3087500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2996100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3162500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2995400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2840900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>590800</v>
+        <v>671000</v>
       </c>
       <c r="E62" s="3">
-        <v>718900</v>
+        <v>693400</v>
       </c>
       <c r="F62" s="3">
-        <v>716400</v>
+        <v>800000</v>
       </c>
       <c r="G62" s="3">
-        <v>710500</v>
+        <v>797200</v>
       </c>
       <c r="H62" s="3">
-        <v>730100</v>
+        <v>790600</v>
       </c>
       <c r="I62" s="3">
-        <v>809200</v>
+        <v>812400</v>
       </c>
       <c r="J62" s="3">
+        <v>900500</v>
+      </c>
+      <c r="K62" s="3">
         <v>809400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>844300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1233200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1200600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1262100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1277500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1164400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1444200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1537400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1711600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1663500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1441800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1418300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1393600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1472600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1362100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1360700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5648,8 +5796,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5746,8 +5897,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5844,106 +5998,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13054000</v>
+        <v>15325800</v>
       </c>
       <c r="E66" s="3">
-        <v>13362500</v>
+        <v>14527200</v>
       </c>
       <c r="F66" s="3">
-        <v>12725900</v>
+        <v>14870400</v>
       </c>
       <c r="G66" s="3">
-        <v>12096500</v>
+        <v>14162000</v>
       </c>
       <c r="H66" s="3">
-        <v>12004100</v>
+        <v>13461600</v>
       </c>
       <c r="I66" s="3">
-        <v>11978700</v>
+        <v>13358800</v>
       </c>
       <c r="J66" s="3">
+        <v>13330600</v>
+      </c>
+      <c r="K66" s="3">
         <v>11429100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11640400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11083100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11040200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10858200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11138400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10620400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11739800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12100800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13401500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13234500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14525700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13713800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13304000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13093300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14506700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13411300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5978,8 +6138,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6076,8 +6237,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6174,8 +6338,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6272,8 +6439,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6370,106 +6540,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2584900</v>
+        <v>2952100</v>
       </c>
       <c r="E72" s="3">
-        <v>2252900</v>
+        <v>2876600</v>
       </c>
       <c r="F72" s="3">
-        <v>2212700</v>
+        <v>2507100</v>
       </c>
       <c r="G72" s="3">
-        <v>2420000</v>
+        <v>2462400</v>
       </c>
       <c r="H72" s="3">
-        <v>2426000</v>
+        <v>2693100</v>
       </c>
       <c r="I72" s="3">
-        <v>2330600</v>
+        <v>2699800</v>
       </c>
       <c r="J72" s="3">
+        <v>2593700</v>
+      </c>
+      <c r="K72" s="3">
         <v>2180400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2178900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2129300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1860900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1957200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2034500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2173600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2286100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2332000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2685700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2877600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2848900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2849600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2798900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3119500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2912600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2781500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6566,8 +6742,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6664,8 +6843,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6762,106 +6944,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4045500</v>
+        <v>4663400</v>
       </c>
       <c r="E76" s="3">
-        <v>3628800</v>
+        <v>4502000</v>
       </c>
       <c r="F76" s="3">
-        <v>3584500</v>
+        <v>4038400</v>
       </c>
       <c r="G76" s="3">
-        <v>3730800</v>
+        <v>3989000</v>
       </c>
       <c r="H76" s="3">
-        <v>3676200</v>
+        <v>4151900</v>
       </c>
       <c r="I76" s="3">
-        <v>3565800</v>
+        <v>4091000</v>
       </c>
       <c r="J76" s="3">
+        <v>3968200</v>
+      </c>
+      <c r="K76" s="3">
         <v>3448000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3503500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3356400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3013700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3128900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3222500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3299200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3225400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3314600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3771700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4014100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4182100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4204800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4205800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4578100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4386000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4244700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6958,209 +7146,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>247900</v>
+        <v>109200</v>
       </c>
       <c r="E81" s="3">
-        <v>62900</v>
+        <v>275900</v>
       </c>
       <c r="F81" s="3">
-        <v>-206900</v>
+        <v>70000</v>
       </c>
       <c r="G81" s="3">
-        <v>58000</v>
+        <v>-230300</v>
       </c>
       <c r="H81" s="3">
-        <v>3300</v>
+        <v>64500</v>
       </c>
       <c r="I81" s="3">
-        <v>183400</v>
+        <v>3700</v>
       </c>
       <c r="J81" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K81" s="3">
         <v>116800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>80700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>97500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-120700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>122500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>77400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-75600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>154400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>141400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-57200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>130100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>68500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>29600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>73000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>161600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7195,106 +7392,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>127400</v>
+        <v>148200</v>
       </c>
       <c r="E83" s="3">
-        <v>111600</v>
+        <v>141700</v>
       </c>
       <c r="F83" s="3">
-        <v>141200</v>
+        <v>124200</v>
       </c>
       <c r="G83" s="3">
-        <v>136500</v>
+        <v>157200</v>
       </c>
       <c r="H83" s="3">
-        <v>136500</v>
+        <v>151900</v>
       </c>
       <c r="I83" s="3">
-        <v>117400</v>
+        <v>151900</v>
       </c>
       <c r="J83" s="3">
+        <v>130700</v>
+      </c>
+      <c r="K83" s="3">
         <v>118500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>128100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>133000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>130100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>139400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>137300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>112000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>111700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>118200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>128300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>139600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>139400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>141400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>135100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>143800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>139000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>136000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>133600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>130900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>128500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>125300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>122800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>119500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>115100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7391,8 +7592,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7489,8 +7693,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7587,8 +7794,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7685,8 +7895,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7783,55 +7996,58 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>826700</v>
+        <v>167700</v>
       </c>
       <c r="E89" s="3">
-        <v>-526200</v>
+        <v>920000</v>
       </c>
       <c r="F89" s="3">
-        <v>44600</v>
+        <v>-585600</v>
       </c>
       <c r="G89" s="3">
-        <v>-143100</v>
+        <v>49700</v>
       </c>
       <c r="H89" s="3">
-        <v>872400</v>
+        <v>-159300</v>
       </c>
       <c r="I89" s="3">
-        <v>-274900</v>
+        <v>970800</v>
       </c>
       <c r="J89" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-51300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-417800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1942400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-353600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-393600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-217400</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="R89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -7881,8 +8097,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7917,55 +8136,56 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25578000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15981000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32106000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29437000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19019000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31195000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-103000</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -8015,8 +8235,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8113,8 +8336,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8211,55 +8437,58 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-55500</v>
+        <v>-185500</v>
       </c>
       <c r="E94" s="3">
-        <v>-210600</v>
+        <v>-61800</v>
       </c>
       <c r="F94" s="3">
-        <v>-166500</v>
+        <v>-234400</v>
       </c>
       <c r="G94" s="3">
-        <v>-140300</v>
+        <v>-185300</v>
       </c>
       <c r="H94" s="3">
-        <v>-154300</v>
+        <v>-156100</v>
       </c>
       <c r="I94" s="3">
-        <v>-113700</v>
+        <v>-171800</v>
       </c>
       <c r="J94" s="3">
+        <v>-126500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-72800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-162000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-125500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-105300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-99800</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8309,8 +8538,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8345,50 +8577,51 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1400</v>
+        <v>-33800</v>
       </c>
       <c r="E96" s="3">
-        <v>-20100</v>
+        <v>-1600</v>
       </c>
       <c r="F96" s="3">
-        <v>-4500</v>
+        <v>-22400</v>
       </c>
       <c r="G96" s="3">
-        <v>-59500</v>
+        <v>-5100</v>
       </c>
       <c r="H96" s="3">
-        <v>-2600</v>
+        <v>-66200</v>
       </c>
       <c r="I96" s="3">
-        <v>-29500</v>
+        <v>-2800</v>
       </c>
       <c r="J96" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-20800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-21300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8443,8 +8676,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8541,8 +8777,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8639,8 +8878,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8737,55 +8979,58 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-853900</v>
+        <v>192500</v>
       </c>
       <c r="E100" s="3">
-        <v>823900</v>
+        <v>-950200</v>
       </c>
       <c r="F100" s="3">
-        <v>100000</v>
+        <v>916900</v>
       </c>
       <c r="G100" s="3">
-        <v>12300</v>
+        <v>111300</v>
       </c>
       <c r="H100" s="3">
-        <v>-422700</v>
+        <v>13700</v>
       </c>
       <c r="I100" s="3">
-        <v>385000</v>
+        <v>-470400</v>
       </c>
       <c r="J100" s="3">
+        <v>428500</v>
+      </c>
+      <c r="K100" s="3">
         <v>181500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>423100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>510300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>128200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>277100</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -8835,55 +9080,58 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-31300</v>
+        <v>-42000</v>
       </c>
       <c r="E101" s="3">
-        <v>18800</v>
+        <v>-34800</v>
       </c>
       <c r="F101" s="3">
-        <v>-19400</v>
+        <v>21000</v>
       </c>
       <c r="G101" s="3">
-        <v>-25800</v>
+        <v>-21500</v>
       </c>
       <c r="H101" s="3">
-        <v>26400</v>
+        <v>-28700</v>
       </c>
       <c r="I101" s="3">
-        <v>35100</v>
+        <v>29400</v>
       </c>
       <c r="J101" s="3">
+        <v>39100</v>
+      </c>
+      <c r="K101" s="3">
         <v>-28400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-45500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2600</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -8933,55 +9181,58 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-114000</v>
+        <v>132800</v>
       </c>
       <c r="E102" s="3">
-        <v>105900</v>
+        <v>-126800</v>
       </c>
       <c r="F102" s="3">
-        <v>-41200</v>
+        <v>117900</v>
       </c>
       <c r="G102" s="3">
-        <v>-296900</v>
+        <v>-45900</v>
       </c>
       <c r="H102" s="3">
-        <v>321700</v>
+        <v>-330400</v>
       </c>
       <c r="I102" s="3">
-        <v>31600</v>
+        <v>358000</v>
       </c>
       <c r="J102" s="3">
+        <v>35200</v>
+      </c>
+      <c r="K102" s="3">
         <v>29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-202300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>264600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>95400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-449100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-37500</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="R102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
@@ -9029,6 +9280,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,446 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>3154000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4403500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3264100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2584400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2877900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3757900</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="3">
         <v>3099700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2612000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2361300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3069000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2457000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2346600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2613400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3233100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2749900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2778900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2564100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4456900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3633800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3545400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3213100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4806500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3837100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3198800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>2547500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3541100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2537300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2425900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2408700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3140200</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3">
         <v>2341900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2084200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1974600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2645300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1965700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1960400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2140300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2819800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2277000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2419600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2374400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3671300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2955100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3016900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2761100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4003100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3097700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2730600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>606500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>862400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>726700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>158500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>469300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>617700</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3">
         <v>757800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>527700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>386700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>423600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>491400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>386200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>473100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>413200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>472900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>359300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>189700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>785600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>678700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>528500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>452100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>803400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>739500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>468200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>506600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>600700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>704100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>533500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>462600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>662000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>561100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1149,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1163,77 +1182,80 @@
       <c r="L12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>101800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>82100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>78900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>107800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>78500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>84900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>69500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>143000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>115100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>116000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>101800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>147100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>115000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>101400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>93800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>129900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>94100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>101300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>85500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>113200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>90400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1333,8 +1355,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1365,39 +1390,39 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>110500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>30500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>21700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1413,15 +1438,15 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>116000</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1434,31 +1459,34 @@
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1535,8 +1563,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1569,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>3033800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4080800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3025600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2890400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2805100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3747400</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
         <v>2744400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2444600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2330400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3058200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2380700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2353200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2477100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3354700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2617100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2818900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2740400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4183100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3452300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3475600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3203200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4545400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3569100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3186200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>120200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>322800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>238500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-306000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>72800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="3">
         <v>355400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>167400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>31000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>76300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>136300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-121600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>132800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-176200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>273800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>181500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>69800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>261100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>268000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>64600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>102000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>141900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>101300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>44400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>204800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>127600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1808,210 +1846,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>63500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>31600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-121000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-45000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-23100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="3">
         <v>-98500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>40500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>17900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>64600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-45800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-62200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-41800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-79300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-73400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>98500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>332000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>496100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>241600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-193900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>258100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>139300</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="3">
         <v>387500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>280200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>199600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>157900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>204500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>128900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>269200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>252100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>16700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>367600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>258700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>209800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>103200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>325600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>333600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>65900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>218200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>190700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>243500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>218900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>177900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>246600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>341100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2042,279 +2087,288 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>5600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>6100</v>
       </c>
       <c r="AE22" s="3">
         <v>6100</v>
       </c>
       <c r="AF22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AG22" s="3">
         <v>6000</v>
       </c>
       <c r="AH22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>6700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>183800</v>
-      </c>
-      <c r="E23" s="3">
-        <v>354400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>117400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-351000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>106300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="3">
         <v>256900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>161700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>71500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>68700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>125400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-109900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>133400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-120400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>220700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>110800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>59700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>172900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>185600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-77500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>77700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>52700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>108900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>87500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>49100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>121200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>219400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>70600</v>
-      </c>
-      <c r="E24" s="3">
-        <v>76400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>42400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-124800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>39200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="3">
         <v>48900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>36100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-76400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>30200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>92100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-20200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>93700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>30000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>32800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>35700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>51200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>68700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>43200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2414,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>113200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>277900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>75100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-226200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>67100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>11100</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3">
         <v>208000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>118900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>39100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>87500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>103100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-117600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>127000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>80800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>45500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>160400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>149900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>135900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>40200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>74000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>33300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>78000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>165300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>109200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>275900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>70000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-230300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>64500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K27" s="3">
         <v>204100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>116800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>80700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-38000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>97500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-120700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>122500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>77400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>41500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>154400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>141400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>130100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>68500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>29600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>73000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>161600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2717,31 +2780,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2818,8 +2884,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2919,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3020,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-63500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-31600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>121000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>45000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-33500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>23100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="3">
         <v>98500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-40500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-17900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-64600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>45800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>62200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>41800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>79300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>73400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>82700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>42200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>26800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>77600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>109200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>275900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>70000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-230300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>64500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="3">
         <v>204100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>116800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>80700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-38000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>97500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-120700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>122500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>77400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>41500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>154400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>141400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>130100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>33100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>68500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>29600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>73000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>161600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3323,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>109200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>275900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>70000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-230300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>64500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="3">
         <v>204100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>116800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>80700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-38000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>97500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-120700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>122500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>77400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>41500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>154400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>141400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>130100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>33100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>68500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>29600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>73000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>161600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3567,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3604,145 +3695,149 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>730300</v>
+        <v>889200</v>
       </c>
       <c r="E41" s="3">
-        <v>597500</v>
+        <v>639400</v>
       </c>
       <c r="F41" s="3">
-        <v>724300</v>
+        <v>556400</v>
       </c>
       <c r="G41" s="3">
-        <v>606400</v>
+        <v>723700</v>
       </c>
       <c r="H41" s="3">
-        <v>652300</v>
+        <v>571900</v>
       </c>
       <c r="I41" s="3">
-        <v>982800</v>
+        <v>635500</v>
       </c>
       <c r="J41" s="3">
+        <v>1041300</v>
+      </c>
+      <c r="K41" s="3">
         <v>624800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>529800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>529100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1480600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>517000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>436900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>897100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>898300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1006600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1193300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1464500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>934800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>677900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>383600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>407000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>714100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>473500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>533400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>527700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>638500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>455700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>410800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>436300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>491300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>474100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>104200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>78300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>97600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>76000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>65900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>76300</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>103500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>55700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>84800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70400</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3755,8 +3850,8 @@
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3806,448 +3901,463 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5552200</v>
+        <v>3994400</v>
       </c>
       <c r="E43" s="3">
-        <v>5821200</v>
+        <v>4076700</v>
       </c>
       <c r="F43" s="3">
-        <v>4951400</v>
+        <v>4516800</v>
       </c>
       <c r="G43" s="3">
-        <v>4544800</v>
+        <v>3994600</v>
       </c>
       <c r="H43" s="3">
-        <v>4437900</v>
+        <v>3421500</v>
       </c>
       <c r="I43" s="3">
-        <v>4475600</v>
+        <v>3412900</v>
       </c>
       <c r="J43" s="3">
+        <v>3542700</v>
+      </c>
+      <c r="K43" s="3">
         <v>4406800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3571300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3538700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6216000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3048600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2900600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2986800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3239000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3474100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3362100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3641000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4139300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4957300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4749700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4250400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4073400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5283800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4529800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5504800</v>
+        <v>5728900</v>
       </c>
       <c r="E44" s="3">
-        <v>5042500</v>
+        <v>4819700</v>
       </c>
       <c r="F44" s="3">
-        <v>5516300</v>
+        <v>4695400</v>
       </c>
       <c r="G44" s="3">
-        <v>5348800</v>
+        <v>5511700</v>
       </c>
       <c r="H44" s="3">
-        <v>5106200</v>
+        <v>5043800</v>
       </c>
       <c r="I44" s="3">
-        <v>4902100</v>
+        <v>4974100</v>
       </c>
       <c r="J44" s="3">
+        <v>5193800</v>
+      </c>
+      <c r="K44" s="3">
         <v>5179300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4481400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4455300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8460400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4786300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4723100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4566000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4669100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5015600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5136400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5615900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5564900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6074600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5759800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5787500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5697000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6032500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5635200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1087400</v>
+        <v>2308500</v>
       </c>
       <c r="E45" s="3">
-        <v>721700</v>
+        <v>1827800</v>
       </c>
       <c r="F45" s="3">
-        <v>855400</v>
+        <v>1648700</v>
       </c>
       <c r="G45" s="3">
-        <v>811100</v>
+        <v>1904900</v>
       </c>
       <c r="H45" s="3">
-        <v>867500</v>
+        <v>1700700</v>
       </c>
       <c r="I45" s="3">
-        <v>712700</v>
+        <v>1819500</v>
       </c>
       <c r="J45" s="3">
+        <v>2035200</v>
+      </c>
+      <c r="K45" s="3">
         <v>833200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>675700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>706900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1156000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>815400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>741800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>571100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>307100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>499700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>442900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>528600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>450900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>604200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>561800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>592100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>435700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>816100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>761300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>773600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>655800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>847500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>969300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12978900</v>
+        <v>12921000</v>
       </c>
       <c r="E46" s="3">
-        <v>12261200</v>
+        <v>11363600</v>
       </c>
       <c r="F46" s="3">
-        <v>12145000</v>
+        <v>11417300</v>
       </c>
       <c r="G46" s="3">
-        <v>11387100</v>
+        <v>12134900</v>
       </c>
       <c r="H46" s="3">
-        <v>11129900</v>
+        <v>10737800</v>
       </c>
       <c r="I46" s="3">
-        <v>11149500</v>
+        <v>10842000</v>
       </c>
       <c r="J46" s="3">
+        <v>11813000</v>
+      </c>
+      <c r="K46" s="3">
         <v>11147600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9314000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9314700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8766200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9167300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8802400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9020900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9113500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9995900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10134700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11250000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11089900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12314000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11454800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11037000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10920200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12605900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11459600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1315900</v>
+        <v>1421700</v>
       </c>
       <c r="E47" s="3">
-        <v>1219200</v>
+        <v>1358700</v>
       </c>
       <c r="F47" s="3">
-        <v>1195500</v>
+        <v>1355500</v>
       </c>
       <c r="G47" s="3">
-        <v>1202000</v>
+        <v>1488000</v>
       </c>
       <c r="H47" s="3">
-        <v>1153100</v>
+        <v>1425300</v>
       </c>
       <c r="I47" s="3">
-        <v>1048400</v>
+        <v>1425200</v>
       </c>
       <c r="J47" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1061400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>958100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>999500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>928400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4311,210 +4421,219 @@
       <c r="AI47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4122400</v>
+        <v>4013100</v>
       </c>
       <c r="E48" s="3">
-        <v>3984200</v>
+        <v>3609300</v>
       </c>
       <c r="F48" s="3">
-        <v>3892000</v>
+        <v>3710000</v>
       </c>
       <c r="G48" s="3">
-        <v>3838400</v>
+        <v>3888800</v>
       </c>
       <c r="H48" s="3">
-        <v>3756500</v>
+        <v>3619500</v>
       </c>
       <c r="I48" s="3">
-        <v>3688000</v>
+        <v>3659300</v>
       </c>
       <c r="J48" s="3">
+        <v>3907400</v>
+      </c>
+      <c r="K48" s="3">
         <v>3605300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3256300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3416200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6289100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3037000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3209100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3284500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3199400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3395700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3631100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4025000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4251400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4416300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4465200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4457200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4667300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4563000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4490400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>501200</v>
+        <v>493000</v>
       </c>
       <c r="E49" s="3">
-        <v>494300</v>
+        <v>438800</v>
       </c>
       <c r="F49" s="3">
-        <v>483700</v>
+        <v>460300</v>
       </c>
       <c r="G49" s="3">
-        <v>483600</v>
+        <v>483300</v>
       </c>
       <c r="H49" s="3">
-        <v>487600</v>
+        <v>456000</v>
       </c>
       <c r="I49" s="3">
-        <v>470400</v>
+        <v>475000</v>
       </c>
       <c r="J49" s="3">
+        <v>498400</v>
+      </c>
+      <c r="K49" s="3">
         <v>442300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>395500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>415200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>411300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>151800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>159400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>162400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>159000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>161900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>173300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>187600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>188200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>172900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>172200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>163500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>161400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>153300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>149800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>147200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>146200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>139900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>140700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>135000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>135600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>129900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4614,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4715,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1070800</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>1070400</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>1192600</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>1240000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>1086400</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>1093600</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>1042100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>953200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>998300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2702900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1706800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1826200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1903300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1457600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1421800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1488900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1726200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1735300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1816600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1839200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1865000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1936100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1603200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1588900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4917,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19989200</v>
+        <v>19678600</v>
       </c>
       <c r="E54" s="3">
-        <v>19029200</v>
+        <v>17501400</v>
       </c>
       <c r="F54" s="3">
-        <v>18908800</v>
+        <v>17719600</v>
       </c>
       <c r="G54" s="3">
-        <v>18151000</v>
+        <v>18893100</v>
       </c>
       <c r="H54" s="3">
-        <v>17613500</v>
+        <v>17116000</v>
       </c>
       <c r="I54" s="3">
-        <v>17449800</v>
+        <v>17157900</v>
       </c>
       <c r="J54" s="3">
+        <v>18488300</v>
+      </c>
+      <c r="K54" s="3">
         <v>17298800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14877100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15143900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14439500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14053900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13987200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14360900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13919600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14965300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15415400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17173200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17248600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18707700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17918500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17509700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17671400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18892700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17656100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5055,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5092,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3636900</v>
+        <v>3596000</v>
       </c>
       <c r="E57" s="3">
-        <v>3704300</v>
+        <v>3184200</v>
       </c>
       <c r="F57" s="3">
-        <v>3383100</v>
+        <v>3449400</v>
       </c>
       <c r="G57" s="3">
-        <v>3240500</v>
+        <v>3380300</v>
       </c>
       <c r="H57" s="3">
-        <v>3101400</v>
+        <v>3055800</v>
       </c>
       <c r="I57" s="3">
-        <v>3211000</v>
+        <v>3021200</v>
       </c>
       <c r="J57" s="3">
+        <v>3402100</v>
+      </c>
+      <c r="K57" s="3">
         <v>3075300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2538500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2548400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4941500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2174500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2173700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2313900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2518000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2447800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2367500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2621900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3274500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3083100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2942400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3095300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3558300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3258700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3116400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3832200</v>
+        <v>4455100</v>
       </c>
       <c r="E58" s="3">
-        <v>3093600</v>
+        <v>3355300</v>
       </c>
       <c r="F58" s="3">
-        <v>4061500</v>
+        <v>2999500</v>
       </c>
       <c r="G58" s="3">
-        <v>3342100</v>
+        <v>4058200</v>
       </c>
       <c r="H58" s="3">
-        <v>2909400</v>
+        <v>3151500</v>
       </c>
       <c r="I58" s="3">
-        <v>2288000</v>
+        <v>2834200</v>
       </c>
       <c r="J58" s="3">
+        <v>2559000</v>
+      </c>
+      <c r="K58" s="3">
         <v>2930600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2317200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2187200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3378000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1223400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1279500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1016400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1224000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1345800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1415400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1634900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1653900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2582000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1721200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1287200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1060400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2197400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1264300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>976200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4479300</v>
+        <v>3957500</v>
       </c>
       <c r="E59" s="3">
-        <v>4146700</v>
+        <v>3921800</v>
       </c>
       <c r="F59" s="3">
-        <v>3644600</v>
+        <v>3742400</v>
       </c>
       <c r="G59" s="3">
-        <v>3929500</v>
+        <v>3641500</v>
       </c>
       <c r="H59" s="3">
-        <v>3549200</v>
+        <v>3705400</v>
       </c>
       <c r="I59" s="3">
-        <v>3792500</v>
+        <v>3457400</v>
       </c>
       <c r="J59" s="3">
+        <v>3883400</v>
+      </c>
+      <c r="K59" s="3">
         <v>3239200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2885200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3042600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4901600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3758300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3306200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3568900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2763500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3549100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3645000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3728900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3421000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4249500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4400600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4389200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3687000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4536000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4683500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11948400</v>
+        <v>12008600</v>
       </c>
       <c r="E60" s="3">
-        <v>10944600</v>
+        <v>10461300</v>
       </c>
       <c r="F60" s="3">
-        <v>11089200</v>
+        <v>10191300</v>
       </c>
       <c r="G60" s="3">
-        <v>10512100</v>
+        <v>11080000</v>
       </c>
       <c r="H60" s="3">
-        <v>9560000</v>
+        <v>9912700</v>
       </c>
       <c r="I60" s="3">
-        <v>9291500</v>
+        <v>9312700</v>
       </c>
       <c r="J60" s="3">
+        <v>9844400</v>
+      </c>
+      <c r="K60" s="3">
         <v>9245000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7741000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7778200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7036600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7156200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6759400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6899100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6505500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7342700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7428000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7985700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8349500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9914600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9064200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8771700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8305700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2557400</v>
+        <v>2384300</v>
       </c>
       <c r="E61" s="3">
-        <v>2744000</v>
+        <v>2239100</v>
       </c>
       <c r="F61" s="3">
-        <v>2835500</v>
+        <v>2588600</v>
       </c>
       <c r="G61" s="3">
-        <v>2711300</v>
+        <v>2833100</v>
       </c>
       <c r="H61" s="3">
-        <v>2965600</v>
+        <v>2556700</v>
       </c>
       <c r="I61" s="3">
-        <v>3108100</v>
+        <v>2888900</v>
       </c>
       <c r="J61" s="3">
+        <v>3348100</v>
+      </c>
+      <c r="K61" s="3">
         <v>3054400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2760600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2896400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2978600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2553900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2705600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2831300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2826800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2831300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3012800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3572900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3081100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3024000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3087500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2996100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3162500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2995400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2840900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>671000</v>
+        <v>125300</v>
       </c>
       <c r="E62" s="3">
-        <v>693400</v>
+        <v>112300</v>
       </c>
       <c r="F62" s="3">
-        <v>800000</v>
+        <v>114300</v>
       </c>
       <c r="G62" s="3">
-        <v>797200</v>
+        <v>121900</v>
       </c>
       <c r="H62" s="3">
-        <v>790600</v>
+        <v>118100</v>
       </c>
       <c r="I62" s="3">
-        <v>812400</v>
+        <v>121700</v>
       </c>
       <c r="J62" s="3">
+        <v>110800</v>
+      </c>
+      <c r="K62" s="3">
         <v>900500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>809400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>844300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1233200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1200600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1262100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1277500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1164400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1444200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1537400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1711600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1663500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1441800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1418300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1393600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1472600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1362100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1360700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5799,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5900,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6001,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>15325800</v>
+        <v>15058100</v>
       </c>
       <c r="E66" s="3">
-        <v>14527200</v>
+        <v>13287900</v>
       </c>
       <c r="F66" s="3">
-        <v>14870400</v>
+        <v>13392100</v>
       </c>
       <c r="G66" s="3">
-        <v>14162000</v>
+        <v>14712400</v>
       </c>
       <c r="H66" s="3">
-        <v>13461600</v>
+        <v>13221100</v>
       </c>
       <c r="I66" s="3">
-        <v>13358800</v>
+        <v>12971800</v>
       </c>
       <c r="J66" s="3">
+        <v>13998300</v>
+      </c>
+      <c r="K66" s="3">
         <v>13330600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11429100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11640400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11083100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11040200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10858200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11138400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10620400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11739800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12100800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13401500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13234500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14525700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13713800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13304000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13093300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14506700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13411300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6139,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6240,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6341,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6442,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6543,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2952100</v>
+        <v>2887000</v>
       </c>
       <c r="E72" s="3">
-        <v>2876600</v>
+        <v>2584600</v>
       </c>
       <c r="F72" s="3">
-        <v>2507100</v>
+        <v>2678600</v>
       </c>
       <c r="G72" s="3">
-        <v>2462400</v>
+        <v>2505100</v>
       </c>
       <c r="H72" s="3">
-        <v>2693100</v>
+        <v>2322000</v>
       </c>
       <c r="I72" s="3">
-        <v>2699800</v>
+        <v>2623500</v>
       </c>
       <c r="J72" s="3">
+        <v>2860500</v>
+      </c>
+      <c r="K72" s="3">
         <v>2593700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2180400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2178900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2129300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1860900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1957200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2034500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2173600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2286100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2332000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2685700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2877600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2848900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2849600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2798900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3119500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2912600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2781500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6745,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6846,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6947,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4663400</v>
+        <v>4466900</v>
       </c>
       <c r="E76" s="3">
-        <v>4502000</v>
+        <v>4083000</v>
       </c>
       <c r="F76" s="3">
-        <v>4038400</v>
+        <v>4192200</v>
       </c>
       <c r="G76" s="3">
-        <v>3989000</v>
+        <v>4035000</v>
       </c>
       <c r="H76" s="3">
-        <v>4151900</v>
+        <v>3761500</v>
       </c>
       <c r="I76" s="3">
-        <v>4091000</v>
+        <v>4044500</v>
       </c>
       <c r="J76" s="3">
+        <v>4334500</v>
+      </c>
+      <c r="K76" s="3">
         <v>3968200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3448000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3503500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3356400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3013700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3128900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3222500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3299200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3225400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3314600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3771700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4014100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4182100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4204800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4205800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4578100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4386000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4244700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7149,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>109200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>275900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>70000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-230300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>64500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="3">
         <v>204100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>116800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>80700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-38000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>97500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-120700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>122500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>77400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>41500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>154400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>141400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-57200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>130100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>33100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>68500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>29600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>73000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>161600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7393,8 +7596,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7402,100 +7606,103 @@
         <v>148200</v>
       </c>
       <c r="E83" s="3">
-        <v>141700</v>
+        <v>147900</v>
       </c>
       <c r="F83" s="3">
-        <v>124200</v>
+        <v>160900</v>
       </c>
       <c r="G83" s="3">
-        <v>157200</v>
+        <v>139500</v>
       </c>
       <c r="H83" s="3">
-        <v>151900</v>
+        <v>128400</v>
       </c>
       <c r="I83" s="3">
-        <v>151900</v>
-      </c>
-      <c r="J83" s="3">
+        <v>139900</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K83" s="3">
         <v>130700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>118500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>128100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>133000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>139400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>137300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>112000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>111700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>118200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>128300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>139600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>139400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>141400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>135100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>143800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>139000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>136000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>133600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>130900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>128500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>125300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>122800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>119500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>115100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7696,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7797,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7898,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7999,58 +8218,61 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>167700</v>
+        <v>-422800</v>
       </c>
       <c r="E89" s="3">
-        <v>920000</v>
+        <v>146800</v>
       </c>
       <c r="F89" s="3">
-        <v>-585600</v>
+        <v>856700</v>
       </c>
       <c r="G89" s="3">
-        <v>49700</v>
+        <v>-585100</v>
       </c>
       <c r="H89" s="3">
-        <v>-159300</v>
+        <v>46800</v>
       </c>
       <c r="I89" s="3">
-        <v>970800</v>
+        <v>-155200</v>
       </c>
       <c r="J89" s="3">
+        <v>1028600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-305900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-51300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-417800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1942400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-353600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-393600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-217400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -8100,8 +8322,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8137,58 +8362,59 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-25578000</v>
+        <v>-144500</v>
       </c>
       <c r="E91" s="3">
-        <v>-15981000</v>
+        <v>-140700</v>
       </c>
       <c r="F91" s="3">
-        <v>-32106000</v>
+        <v>-77400</v>
       </c>
       <c r="G91" s="3">
-        <v>-29437000</v>
+        <v>-195800</v>
       </c>
       <c r="H91" s="3">
-        <v>-19019000</v>
+        <v>-145500</v>
       </c>
       <c r="I91" s="3">
-        <v>-31195000</v>
+        <v>-131500</v>
       </c>
       <c r="J91" s="3">
+        <v>-151900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8238,8 +8464,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8339,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8440,58 +8672,61 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-185500</v>
+        <v>-165100</v>
       </c>
       <c r="E94" s="3">
-        <v>-61800</v>
+        <v>-162400</v>
       </c>
       <c r="F94" s="3">
-        <v>-234400</v>
+        <v>-57600</v>
       </c>
       <c r="G94" s="3">
-        <v>-185300</v>
+        <v>-234200</v>
       </c>
       <c r="H94" s="3">
-        <v>-156100</v>
+        <v>-174800</v>
       </c>
       <c r="I94" s="3">
-        <v>-171800</v>
+        <v>-152100</v>
       </c>
       <c r="J94" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-126500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-72800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-162000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-125500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-105300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8541,8 +8776,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8578,53 +8816,54 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-33800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-22400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-66200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
         <v>-32900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-20800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-21300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8679,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8780,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8881,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8982,58 +9230,61 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>192500</v>
+        <v>675500</v>
       </c>
       <c r="E100" s="3">
-        <v>-950200</v>
+        <v>168600</v>
       </c>
       <c r="F100" s="3">
-        <v>916900</v>
+        <v>-884800</v>
       </c>
       <c r="G100" s="3">
-        <v>111300</v>
+        <v>916200</v>
       </c>
       <c r="H100" s="3">
-        <v>13700</v>
+        <v>105000</v>
       </c>
       <c r="I100" s="3">
-        <v>-470400</v>
+        <v>13300</v>
       </c>
       <c r="J100" s="3">
+        <v>-498400</v>
+      </c>
+      <c r="K100" s="3">
         <v>428500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>181500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>423100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>510300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>128200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>277100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -9083,58 +9334,61 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-42000</v>
+        <v>-20300</v>
       </c>
       <c r="E101" s="3">
-        <v>-34800</v>
+        <v>-28000</v>
       </c>
       <c r="F101" s="3">
-        <v>21000</v>
+        <v>31100</v>
       </c>
       <c r="G101" s="3">
-        <v>-21500</v>
+        <v>41800</v>
       </c>
       <c r="H101" s="3">
-        <v>-28700</v>
+        <v>-30700</v>
       </c>
       <c r="I101" s="3">
-        <v>29400</v>
-      </c>
-      <c r="J101" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K101" s="3">
         <v>39100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-45500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -9184,58 +9438,61 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>132800</v>
+        <v>171300</v>
       </c>
       <c r="E102" s="3">
-        <v>-126800</v>
+        <v>116300</v>
       </c>
       <c r="F102" s="3">
-        <v>117900</v>
+        <v>-118100</v>
       </c>
       <c r="G102" s="3">
-        <v>-45900</v>
+        <v>117800</v>
       </c>
       <c r="H102" s="3">
-        <v>-330400</v>
+        <v>-43300</v>
       </c>
       <c r="I102" s="3">
-        <v>358000</v>
+        <v>-321900</v>
       </c>
       <c r="J102" s="3">
+        <v>379300</v>
+      </c>
+      <c r="K102" s="3">
         <v>35200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-202300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>264600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>95400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-449100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -9283,6 +9540,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -826,86 +829,89 @@
       <c r="J8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
         <v>3099700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2612000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2361300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3069000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2457000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2346600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2613400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3233100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2749900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2778900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2564100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4456900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3633800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3545400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3213100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4806500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3837100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3198800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -930,86 +936,89 @@
       <c r="J9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
         <v>2341900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2084200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1974600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2645300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1965700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1960400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2140300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2819800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2277000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2419600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2374400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3671300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2955100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3016900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2761100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4003100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3097700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2730600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1034,86 +1043,89 @@
       <c r="J10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
         <v>757800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>527700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>386700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>423600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>491400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>386200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>473100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>413200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>472900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>359300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>189700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>785600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>678700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>528500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>452100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>803400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>739500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>468200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>506600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>600700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>704100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>533500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>462600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>662000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>561100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,77 +1198,80 @@
       <c r="M12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3">
         <v>101800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>82100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>78900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>65300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>107800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>78500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>84900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>69500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>143000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>115100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>116000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>101800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>147100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>115000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>101400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>93800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>129900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>94100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>101300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>85500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>113200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>90400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1358,8 +1374,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1393,39 +1412,39 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>110500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>30500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>21700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1441,15 +1460,15 @@
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>116000</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1462,8 +1481,11 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1488,8 +1510,8 @@
       <c r="J15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1566,8 +1588,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,8 +1626,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1627,86 +1653,89 @@
       <c r="J17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3">
         <v>2744400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2444600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2330400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3058200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2380700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2353200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2477100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3354700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2617100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2818900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2740400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4183100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3452300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3475600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3203200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4545400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3569100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3186200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1731,86 +1760,89 @@
       <c r="J18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
         <v>355400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>167400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>136300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-121600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>132800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-176200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>273800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>181500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>69800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>261100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>268000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>64600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>102000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>141900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>101300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>44400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>204800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>127600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,8 +1879,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1873,86 +1906,89 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>-98500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>40500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>17900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>21700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>64600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-45800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-62200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-41800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-79300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-73400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>10800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>98500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1977,86 +2013,89 @@
       <c r="J21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
         <v>387500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>280200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>199600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>157900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>204500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>128900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>269200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>252100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>367600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>258700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>209800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>103200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>325600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>333600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>65900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>218200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>190700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>243500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>218900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>177900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>246600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>341100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2090,77 +2129,80 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3">
         <v>5600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>6100</v>
       </c>
       <c r="AF22" s="3">
         <v>6100</v>
       </c>
       <c r="AG22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AH22" s="3">
         <v>6000</v>
       </c>
       <c r="AI22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2185,86 +2227,89 @@
       <c r="J23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="3">
         <v>256900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>161700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>71500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>68700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>125400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-109900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>133400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-25500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-120400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>220700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>110800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>59700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-40200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>172900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>185600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-77500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>77700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>52700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>108900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>87500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>49100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>121200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>219400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2289,86 +2334,89 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3">
         <v>48900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>42800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-76400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>30200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>92100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-20200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>93700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>30000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>32800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>51200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>68700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>43200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>54100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,8 +2519,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2497,86 +2548,89 @@
       <c r="J26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="3">
         <v>208000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>118900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>87500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>103100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-117600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>127000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>80800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>45500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>160400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>149900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>135900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>40200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>74000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>33300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>78000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>165300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2601,86 +2655,89 @@
       <c r="J27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
         <v>204100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>116800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>22800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>80700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-38000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>97500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-120700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>122500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>77400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>41500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-75600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>154400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>141400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>130100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>33100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>68500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>29600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>73000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>161600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,8 +2869,8 @@
       <c r="J29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,8 +3161,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3121,86 +3190,89 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>98500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-40500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-17900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-21700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-64600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>45800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>62200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>41800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>79300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>73400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>82700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>42200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>26800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>77600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3225,86 +3297,89 @@
       <c r="J33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="3">
         <v>204100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>116800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>22800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>80700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>97500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-120700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>122500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>77400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>41500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-75600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>154400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>141400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>130100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>33100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>68500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>29600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>73000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>161600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,8 +3482,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3433,195 +3511,201 @@
       <c r="J35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="3">
         <v>204100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>116800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>22800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>80700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>97500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-120700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>122500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>77400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>41500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-75600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>154400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>141400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>130100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>33100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>68500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>29600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>73000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>161600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,117 +3781,121 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>820800</v>
+      </c>
+      <c r="E41" s="3">
         <v>889200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>639400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>556400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>723700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>571900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>635500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1041300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>624800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>529800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>529100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1480600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>517000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>436900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>897100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>898300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1006600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1193300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1464500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>934800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>677900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>383600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>407000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>714100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>473500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>533400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>527700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>638500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>455700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>410800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>436300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>491300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>474100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>103400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3827,20 +3916,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>103500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>55700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>84800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>70400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3853,8 +3942,8 @@
       <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3904,463 +3993,478 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5617100</v>
+      </c>
+      <c r="E43" s="3">
         <v>3994400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4076700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4516800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3994600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3421500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3412900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3542700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4406800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3571300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3538700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6216000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3048600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2900600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2986800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3239000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3474100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3362100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3641000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4139300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4957300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4749700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4250400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4073400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5283800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4529800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5489300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5728900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4819700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4695400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5511700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5043800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4974100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5193800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5179300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4481400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4455300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8460400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4786300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4723100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4566000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4669100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5015600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5136400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5615900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5564900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6074600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5759800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5787500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5697000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6032500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5635200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1062800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2308500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1827800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1648700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1904900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1819500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2035200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>833200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>675700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>706900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1156000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>815400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>741800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>571100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>307100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>499700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>442900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>528600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>450900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>604200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>561800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>592100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>435700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>816100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>761300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>773600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>655800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>847500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>969300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13093400</v>
+      </c>
+      <c r="E46" s="3">
         <v>12921000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11363600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11417300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12134900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10737800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10842000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11813000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11147600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9314000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9314700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8766200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9167300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8802400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9020900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9113500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9995900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10134700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11250000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11089900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12314000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11454800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11037000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10920200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12605900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11459600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1184800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1421700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1358700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1355500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1488000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1425300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1425200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1440000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1061400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>958100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>999500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>928400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4424,216 +4528,225 @@
       <c r="AJ47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3670300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4013100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3609300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3710000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3888800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3619500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3659300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3907400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3605300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3256300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3416200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6289100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3037000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3209100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3284500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3199400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3395700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3631100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4025000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4251400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4416300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4465200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4457200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4667300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4563000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4490400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>456300</v>
+      </c>
+      <c r="E49" s="3">
         <v>493000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>438800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>460300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>483300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>456000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>475000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>498400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>442300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>395500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>415200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>411300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>151800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>159400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>162400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>159000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>161900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>173300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>187600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>188200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>172900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>172200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>163500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>161400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>153300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>149800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>147200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>146200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>139900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>140700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>135000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>135600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>129900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,13 +4956,16 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>200300</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -4867,85 +4986,88 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>1042100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>953200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>998300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2702900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1706800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1826200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1903300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1457600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1421800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1488900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1726200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1735300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1816600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1839200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1865000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1936100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1603200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1588900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19372700</v>
+      </c>
+      <c r="E54" s="3">
         <v>19678600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17501400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17719600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18893100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17116000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17157900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18488300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17298800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14877100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15143900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14439500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14053900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13987200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14360900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13919600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14965300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15415400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17173200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17248600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18707700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17918500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17509700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17671400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18892700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17656100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3548900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3596000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3184200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3449400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3380300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3055800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3021200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3402100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3075300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2538500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2548400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4941500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2174500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2173700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2313900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2518000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2447800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2367500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2621900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3274500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3083100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2942400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3095300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3558300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3258700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3116400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4757600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4455100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3355300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2999500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4058200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3151500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2834200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2559000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2930600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2317200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2187200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3378000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1223400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1279500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1016400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1224000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1345800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1415400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1634900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1653900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2582000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1721200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1287200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1060400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2197400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1264300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>976200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3881700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3957500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3921800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3742400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3641500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3705400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3457400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3883400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3239200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2885200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3042600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4901600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3758300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3306200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3568900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2763500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3549100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3645000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3728900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3421000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4249500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4400600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4389200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3687000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4536000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4683500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12188200</v>
+      </c>
+      <c r="E60" s="3">
         <v>12008600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10461300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10191300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11080000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9912700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9312700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9844400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9245000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7741000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7778200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7036600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7156200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6759400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6899100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6505500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7342700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7428000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7985700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8349500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9914600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9064200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8771700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8305700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2175300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2384300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2239100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2588600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2833100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2556700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2888900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3348100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3054400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2760600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2896400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2978600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2553900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2705600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2831300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2826800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2831300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3012800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3572900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3081100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3024000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3087500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2996100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3162500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2995400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2840900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E62" s="3">
         <v>125300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>112300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>114300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>121900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>118100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>110800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>809400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>844300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1233200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1200600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1262100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1277500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1164400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1444200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1537400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1711600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1663500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1441800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1418300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1393600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1472600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1362100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1360700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14982000</v>
+      </c>
+      <c r="E66" s="3">
         <v>15058100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13287900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13392100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14712400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13221100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12971800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13998300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13330600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11429100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11640400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11083100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11040200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10858200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11138400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10620400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11739800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12100800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13401500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13234500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14525700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13713800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13304000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13093300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14506700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13411300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2750500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2887000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2584600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2678600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2505100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2322000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2623500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2860500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2593700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2180400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2178900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2129300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1860900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1957200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2034500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2173600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2286100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2332000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2685700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2877600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2848900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2849600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2798900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3119500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2912600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2781500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4247400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4466900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4083000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4192200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4035000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3761500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4044500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4334500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3968200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3448000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3503500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3356400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3013700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3128900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3222500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3299200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3225400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3314600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3771700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4014100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4182100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4204800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4205800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4578100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4386000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4244700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,117 +7534,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7481,86 +7675,89 @@
       <c r="J81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81" s="3">
         <v>204100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>116800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>22800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>80700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>97500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-120700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>122500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>77400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>41500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-75600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>154400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>141400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-57200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>130100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>33100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>68500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>29600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>73000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>161600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E83" s="3">
         <v>148200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>147900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>160900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>139500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>128400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>139900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L83" s="3">
         <v>130700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>118500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>128100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>133000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>130100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>139400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>137300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>112000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>111700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>118200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>128300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>139600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>139400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>141400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>135100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>143800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>139000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>136000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>133600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>130900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>128500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>125300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>122800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>119500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>115100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,61 +8434,64 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-262300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-422800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>146800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>856700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-585100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>46800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-155200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1028600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-305900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-51300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-417800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1942400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-353600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-393600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-217400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -8325,8 +8541,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,61 +8582,62 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-153500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-144500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-140700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-195800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-145500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-131500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-151900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-103000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8467,8 +8687,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,61 +8901,64 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-165100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-162400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-234200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-174800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-152100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-182000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-126500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-72800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-162000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-125500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-105300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-99800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8779,8 +9008,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8843,30 +9076,30 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3">
         <v>-32900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-20800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-21300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8921,8 +9154,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,61 +9475,64 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>510600</v>
+      </c>
+      <c r="E100" s="3">
         <v>675500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>168600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-884800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>916200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>105000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-498400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>428500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>181500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>423100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>510300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>128200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>277100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -9337,61 +9582,64 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-20300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-28000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>41800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-30700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-49700</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L101" s="3">
         <v>39100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-45500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2600</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -9441,61 +9689,64 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E102" s="3">
         <v>171300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>116300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-118100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>117800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-321900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>379300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>29000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-202300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>264600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>95400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-449100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -9543,6 +9794,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,155 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,86 +836,89 @@
       <c r="K8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="3">
         <v>3099700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2612000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2361300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3069000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2346600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2613400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3233100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2749900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2778900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2564100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4456900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3633800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3545400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3213100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4806500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3837100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3198800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,86 +946,89 @@
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3">
         <v>2341900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2084200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1974600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2645300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1965700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1960400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2140300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2819800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2277000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2419600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2374400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3671300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2955100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3016900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2761100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4003100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3097700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2730600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1046,86 +1056,89 @@
       <c r="K10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="3">
         <v>757800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>527700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>386700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>423600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>491400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>386200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>473100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>413200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>472900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>359300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>189700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>785600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>678700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>528500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>452100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>803400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>739500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>468200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>506600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>600700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>704100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>533500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>462600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>662000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>561100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,77 +1215,80 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>101800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>82100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>78900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>65300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>107800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>78500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>84900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>69500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>143000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>115100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>116000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>101800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>147100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>115000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>101400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>93800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>129900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>94100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>101300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>85500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>113200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>90400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1377,8 +1394,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1415,39 +1435,39 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
         <v>9100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>110500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>30500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>21700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1463,15 +1483,15 @@
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>116000</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1484,8 +1504,11 @@
       <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1513,8 +1536,8 @@
       <c r="K15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1591,8 +1614,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,8 +1653,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1656,86 +1683,89 @@
       <c r="K17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="3">
         <v>2744400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2444600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2330400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3058200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2380700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2353200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2477100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3354700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2617100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2818900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2740400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4183100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3452300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3475600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3203200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4545400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3569100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3186200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1763,86 +1793,89 @@
       <c r="K18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="3">
         <v>355400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>167400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>76300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>136300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-121600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>132800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-176200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>273800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>181500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>69800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>261100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>268000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>64600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>102000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>141900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>101300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>44400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>204800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>127600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,8 +1913,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1909,86 +1943,89 @@
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3">
         <v>-98500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>40500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>17900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>64600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-45800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-41800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-79300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-73400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>20000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>98500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2016,86 +2053,89 @@
       <c r="K21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="3">
         <v>387500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>280200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>199600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>157900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>204500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>128900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>269200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>252100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>367600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>258700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>209800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>103200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>325600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>333600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>65900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>218200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>190700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>243500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>218900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>177900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>246600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>341100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2132,77 +2172,80 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>5600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>6100</v>
       </c>
       <c r="AG22" s="3">
         <v>6100</v>
       </c>
       <c r="AH22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AI22" s="3">
         <v>6000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>6700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2230,86 +2273,89 @@
       <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3">
         <v>256900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>161700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>71500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>68700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>125400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-109900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>133400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-25500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-120400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>220700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>110800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>59700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>172900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>185600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-77500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>77700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>52700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>108900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>87500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>49100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>121200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>219400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2337,86 +2383,89 @@
       <c r="K24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3">
         <v>48900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>42800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-76400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>30200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>92100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-20200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>93700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>30000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>32800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>35700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>51200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>68700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>15800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>54100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,8 +2571,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2551,86 +2603,89 @@
       <c r="K26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="3">
         <v>208000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>118900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>39100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>87500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>103100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-117600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>127000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>80800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>45500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>160400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>149900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>26500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>135900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>40200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>74000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>33300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>78000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>165300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2658,86 +2713,89 @@
       <c r="K27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="3">
         <v>204100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>116800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>80700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>97500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-120700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>122500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>77400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>41500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-75600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>154400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>141400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>130100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>33100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>68500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>29600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>161600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,8 +2933,8 @@
       <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,8 +3231,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3193,86 +3263,89 @@
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="3">
         <v>98500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-40500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-17900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-64600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>45800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>62200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>41800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>79300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>73400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>82700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>42200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>26800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>77600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3300,86 +3373,89 @@
       <c r="K33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M33" s="3">
         <v>204100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>116800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>80700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>97500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-120700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>122500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>77400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>41500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-75600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>154400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>141400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>130100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>33100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>68500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>29600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>161600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,8 +3561,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3514,198 +3593,204 @@
       <c r="K35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="3">
         <v>204100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>116800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>80700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>97500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-120700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>122500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>77400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>41500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-75600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>154400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>141400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>130100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>33100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>68500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>29600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>161600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,124 +3868,128 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>886700</v>
+      </c>
+      <c r="E41" s="3">
         <v>820800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>889200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>639400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>556400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>723700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>571900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>635500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1041300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>624800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>529800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>529100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1480600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>517000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>436900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>897100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>898300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1006600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1193300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1464500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>934800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>677900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>383600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>407000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>714100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>473500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>533400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>527700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>638500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>455700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>410800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>436300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>491300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>474100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E42" s="3">
         <v>103400</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -3919,20 +4009,20 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>103500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>84800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>70400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3945,8 +4035,8 @@
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3996,478 +4086,493 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6244800</v>
+      </c>
+      <c r="E43" s="3">
         <v>5617100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3994400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4076700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4516800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3994600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3421500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3412900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3542700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4406800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3571300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3538700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6216000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3048600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2900600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2986800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3239000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3474100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3362100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3641000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4139300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4957300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4749700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4250400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4073400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5283800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4529800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5178300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5489300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5728900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4819700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4695400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5511700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5043800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4974100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5193800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5179300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4481400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4455300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8460400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4786300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4723100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4566000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4669100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5015600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5136400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5615900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5564900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6074600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5759800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5787500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5697000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6032500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5635200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1127100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1062800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2308500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1827800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1648700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1904900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1819500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2035200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>833200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>675700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>706900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1156000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>815400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>741800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>571100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>307100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>499700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>442900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>528600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>450900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>604200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>561800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>592100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>435700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>816100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>761300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>773600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>655800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>847500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>969300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13515400</v>
+      </c>
+      <c r="E46" s="3">
         <v>13093400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12921000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11363600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11417300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12134900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10737800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10842000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11813000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11147600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9314000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9314700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8766200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9167300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8802400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9020900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9113500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9995900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10134700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11250000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11089900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12314000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11454800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11037000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10920200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12605900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11459600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1202500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1184800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1421700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1358700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1355500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1488000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1425300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1425200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1440000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1061400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>958100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>999500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>928400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4531,222 +4636,231 @@
       <c r="AK47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3836000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3670300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4013100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3609300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3710000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3888800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3619500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3659300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3907400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3605300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3256300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3416200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6289100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3037000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3209100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3284500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3199400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3395700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3631100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4025000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4251400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4416300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4465200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4457200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4667300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4563000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4490400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>505900</v>
+      </c>
+      <c r="E49" s="3">
         <v>456300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>493000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>438800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>460300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>483300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>456000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>475000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>498400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>442300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>395500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>415200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>411300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>151800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>159400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>162400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>159000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>161900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>173300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>187600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>188200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>172900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>172200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>163500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>161400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>153300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>149800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>147200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>146200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>139900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>140700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>135000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>135600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>129900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,17 +5076,20 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E52" s="3">
         <v>200300</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
@@ -4989,85 +5109,88 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>1042100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>953200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>998300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2702900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1706800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1826200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1903300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1457600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1421800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1488900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1726200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1735300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1816600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1839200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1865000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1936100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1603200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1588900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20146900</v>
+      </c>
+      <c r="E54" s="3">
         <v>19372700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19678600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17501400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17719600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18893100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17116000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17157900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18488300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17298800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14877100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15143900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14439500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14053900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13987200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14360900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13919600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14965300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15415400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17173200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17248600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18707700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17918500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17509700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17671400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18892700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17656100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3965800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3548900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3596000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3184200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3449400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3380300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3055800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3021200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3402100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3075300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2538500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2548400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4941500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2174500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2173700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2313900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2518000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2447800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2367500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2621900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3274500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3083100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2942400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3095300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3558300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3258700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3116400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3520600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4757600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4455100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3355300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2999500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4058200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3151500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2834200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2559000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2930600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2317200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2187200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3378000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1223400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1279500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1016400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1224000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1345800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1415400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1634900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1653900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2582000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1721200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1287200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1060400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2197400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1264300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>976200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4849700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3881700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3957500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3921800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3742400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3641500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3705400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3457400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3883400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3239200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2885200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3042600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4901600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3758300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3306200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3568900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2763500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3549100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3645000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3728900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3421000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4249500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4400600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4389200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3687000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4536000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4683500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12336100</v>
+      </c>
+      <c r="E60" s="3">
         <v>12188200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12008600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10461300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10191300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11080000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9912700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9312700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9844400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9245000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7741000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7778200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7036600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7156200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6759400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6899100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6505500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7342700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7428000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7985700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8349500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9914600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9064200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8771700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8305700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2419500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2175300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2384300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2239100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2588600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2833100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2556700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2888900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3348100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3054400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2760600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2896400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2978600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2553900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2705600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2831300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2826800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2831300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3012800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3572900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3081100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3024000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3087500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2996100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3162500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2995400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2840900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E62" s="3">
         <v>113500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>125300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>112300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>114300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>121900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>118100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>121700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>110800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>809400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>844300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1233200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1200600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1262100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1277500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1164400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1444200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1537400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1711600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1663500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1441800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1418300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1393600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1472600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1362100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1360700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15305000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14982000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15058100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13287900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13392100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14712400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13221100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12971800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13998300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13330600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11429100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11640400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11083100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11040200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10858200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11138400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10620400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11739800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12100800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13401500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13234500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14525700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13713800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13304000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13093300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14506700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13411300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3229000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2750500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2887000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2584600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2678600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2505100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2322000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2623500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2860500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2593700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2180400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2178900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2129300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1860900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1957200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2034500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2173600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2286100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2332000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2685700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2877600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2848900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2849600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2798900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3119500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2912600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2781500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4694000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4247400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4466900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4083000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4192200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4035000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3761500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4044500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4334500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3968200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3448000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3503500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3356400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3013700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3128900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3222500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3299200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3225400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3314600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3771700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4014100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4182100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4204800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4205800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4578100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4386000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4244700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,120 +7726,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7678,86 +7873,89 @@
       <c r="K81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M81" s="3">
         <v>204100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>116800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>80700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>97500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-120700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>122500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>77400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>41500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-75600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>154400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>141400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>130100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>33100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>68500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>29600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>161600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E83" s="3">
         <v>124100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>148200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>147900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>160900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>139500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>128400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>139900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M83" s="3">
         <v>130700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>118500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>128100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>133000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>130100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>139400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>137300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>112000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>111700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>118200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>128300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>139600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>139400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>141400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>135100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>143800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>139000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>136000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>133600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>130900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>128500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>125300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>122800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>119500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>115100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,64 +8651,67 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1516800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-262300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-422800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>146800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>856700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-585100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-155200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1028600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-305900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-51300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-417800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1942400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-353600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-393600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-217400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -8544,8 +8761,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,64 +8803,65 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-208400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-153500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-144500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-140700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-195800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-145500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-131500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-151900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-103000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8690,8 +8911,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,64 +9131,67 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-208900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-191700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-165100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-162400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-234200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-174800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-152100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-182000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-126500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-72800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-162000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-125500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-105300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-99800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -9011,8 +9241,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,13 +9283,14 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
+      <c r="D96" s="3">
+        <v>4100</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>10</v>
@@ -9079,30 +9313,30 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
         <v>-32900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-20800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -9157,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,64 +9721,67 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1299300</v>
+      </c>
+      <c r="E100" s="3">
         <v>510600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>675500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>168600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-884800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>916200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>105000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-498400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>428500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>181500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>423100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>510300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>128200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>277100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -9585,64 +9831,67 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E101" s="3">
         <v>20900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-20300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-28000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>41800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-30700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-49700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M101" s="3">
         <v>39100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-28400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-45500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -9692,64 +9941,67 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E102" s="3">
         <v>10500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>171300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>116300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-118100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>117800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-321900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>379300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-202300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>264600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>95400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-449100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-37500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -9797,6 +10049,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KWHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>KWHIY</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,86 +843,89 @@
       <c r="L8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3">
         <v>3099700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2612000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2361300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3069000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2457000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2346600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2613400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3233100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2749900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2778900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2564100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4456900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3633800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3545400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3213100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4806500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3837100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3198800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3125000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4356100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3459100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3384500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3031400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4220200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3066800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3170500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,86 +956,89 @@
       <c r="L9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
         <v>2341900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2084200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1974600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2645300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1965700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1960400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2140300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2819800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2277000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2419600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2374400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3671300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2955100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3016900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2761100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4003100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3097700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2730600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2618400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3755500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2755000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2851000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2568800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3558100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2505800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2794600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,86 +1069,89 @@
       <c r="L10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3">
         <v>757800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>527700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>386700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>423600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>491400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>386200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>473100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>413200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>472900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>359300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>189700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>785600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>678700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>528500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>452100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>803400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>739500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>468200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>506600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>600700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>704100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>533500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>462600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>662000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>561100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>375900</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1218,77 +1232,80 @@
       <c r="O12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3">
         <v>101800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>82100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>78900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>65300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>107800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>78500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>84900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>69500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>143000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>115100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>116000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>101800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>147100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>115000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>101400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>93800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>129900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>94100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>101300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>85500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>113200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>90400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,8 +1414,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1438,39 +1458,39 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>110500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>30500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>21700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1486,15 +1506,15 @@
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>116000</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1507,8 +1527,11 @@
       <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1539,8 +1562,8 @@
       <c r="L15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1617,8 +1640,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,8 +1680,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1686,86 +1713,89 @@
       <c r="L17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3">
         <v>2744400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2444600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2330400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3058200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2380700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2353200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2477100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3354700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2617100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2818900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2740400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4183100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3452300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3475600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3203200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4545400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3569100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3186200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3060400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4254200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3317200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3283200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2987000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4015400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2939200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3236700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1796,86 +1826,89 @@
       <c r="L18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3">
         <v>355400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>167400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>76300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>136300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-121600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>132800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-40000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-176200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>273800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>181500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>69800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>261100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>268000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>64600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>102000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>141900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>101300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>44400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>204800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>127600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,8 +1947,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1946,86 +1980,89 @@
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3">
         <v>-98500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>17900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>21700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>64600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-45800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-62200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-79300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-73400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>20000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-42200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-26800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-77600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>98500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2056,86 +2093,89 @@
       <c r="L21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3">
         <v>387500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>280200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>199600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>157900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>204500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>128900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>269200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>252100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>367600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>258700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>209800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>103200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>325600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>333600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>65900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>218200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>190700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>243500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>218900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>177900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>246600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>341100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2175,77 +2215,80 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7100</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>6100</v>
       </c>
       <c r="AH22" s="3">
         <v>6100</v>
       </c>
       <c r="AI22" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="AJ22" s="3">
         <v>6000</v>
       </c>
       <c r="AK22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>6700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2276,86 +2319,89 @@
       <c r="L23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3">
         <v>256900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>161700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>71500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>68700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>125400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-109900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>133400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-120400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>220700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>110800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>59700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>172900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>185600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-77500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>77700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>52700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>108900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>87500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>49100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>121200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>219400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2386,86 +2432,89 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3">
         <v>48900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>42800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>36100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-76400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>30200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>92100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-20200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>93700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>30000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>32800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>35700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>51200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-83100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>68700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>43200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>54100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,8 +2623,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2606,86 +2658,89 @@
       <c r="L26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3">
         <v>208000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>118900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>32500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>87500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>103100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-117600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>127000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>80800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>45500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>160400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>149900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>26500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>135900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>40200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>74000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>33300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>78000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>165300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-40700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2716,86 +2771,89 @@
       <c r="L27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" s="3">
         <v>204100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>116800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>22800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>80700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>97500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-120700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>122500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>77400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>41500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-75600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>154400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>141400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>130100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>33100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>68500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>73000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>161600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,8 +2997,8 @@
       <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,8 +3301,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3266,86 +3336,89 @@
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3">
         <v>98500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-17900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-21700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-64600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>45800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>62200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>79300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>73400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>82700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>42200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>26800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>77600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-98500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3376,86 +3449,89 @@
       <c r="L33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="3">
         <v>204100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>116800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>22800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>80700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>97500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-120700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>122500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>77400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>41500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-75600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>154400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>141400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>130100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>33100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>68500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>73000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>161600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,8 +3640,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3596,201 +3675,207 @@
       <c r="L35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N35" s="3">
         <v>204100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>116800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>22800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>80700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>97500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-120700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>122500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>77400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>41500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-75600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>154400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>141400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>130100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>33100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>68500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>73000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>161600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,126 +3955,130 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3">
         <v>886700</v>
       </c>
-      <c r="E41" s="3">
-        <v>820800</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="3">
         <v>889200</v>
       </c>
-      <c r="G41" s="3">
-        <v>639400</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="3">
         <v>556400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>723700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>571900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>635500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1041300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>624800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>529800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>529100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1480600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>517000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>436900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>897100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>898300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1006600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1193300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1464500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>934800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>677900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>383600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>407000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>714100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>473500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>533400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>527700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>638500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>455700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>410800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>436300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>491300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>474100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>350100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>103400</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -4012,20 +4102,20 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>103500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>55700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>84800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>70400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
@@ -4038,8 +4128,8 @@
       <c r="U42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -4089,493 +4179,508 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>6244800</v>
+      <c r="D43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E43" s="3">
-        <v>5617100</v>
-      </c>
-      <c r="F43" s="3">
+        <v>5105800</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="3">
         <v>3994400</v>
       </c>
-      <c r="G43" s="3">
-        <v>4076700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3">
         <v>4516800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3994600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3421500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3412900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3542700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4406800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3571300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3538700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6216000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3048600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2900600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2986800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3239000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3474100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3362100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3641000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4139300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4957300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4749700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4250400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4073400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5283800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4529800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4362500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4229500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4971000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4402000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4006900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3920900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4383800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3795500</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
         <v>5178300</v>
       </c>
-      <c r="E44" s="3">
-        <v>5489300</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3">
         <v>5728900</v>
       </c>
-      <c r="G44" s="3">
-        <v>4819700</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3">
         <v>4695400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5511700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5043800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4974100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5193800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5179300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4481400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4455300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8460400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4786300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4723100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4566000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4669100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5015600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5136400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5615900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5564900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6074600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5759800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5787500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5697000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6032500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5635200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5097500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4562800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5051200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4687700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4559700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4300700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4782900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4404100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1127100</v>
+      <c r="D45" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E45" s="3">
-        <v>1062800</v>
-      </c>
-      <c r="F45" s="3">
+        <v>2344700</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3">
         <v>2308500</v>
       </c>
-      <c r="G45" s="3">
-        <v>1827800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>1648700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1904900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1819500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2035200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>833200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>675700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>706900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1156000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>815400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>741800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>571100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>307100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>499700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>442900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>528600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>450900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>604200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>561800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>592100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>435700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>816100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>761300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>773600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>655800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1006500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1066100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1114300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>847500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>969300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>854600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3">
         <v>13515400</v>
       </c>
-      <c r="E46" s="3">
-        <v>13093400</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="3">
         <v>12921000</v>
       </c>
-      <c r="G46" s="3">
-        <v>11363600</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" s="3">
         <v>11417300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12134900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10737800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10842000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11813000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11147600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9314000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9314700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8766200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9167300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8802400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9020900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9113500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9995900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10134700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11250000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11089900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12314000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11454800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11037000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10920200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12605900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11459600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10761400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10086600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11484400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10566600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9560400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>10610100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>9404300</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1202500</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E47" s="3">
-        <v>1184800</v>
-      </c>
-      <c r="F47" s="3">
+        <v>1429400</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3">
         <v>1421700</v>
       </c>
-      <c r="G47" s="3">
-        <v>1358700</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
         <v>1355500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1488000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1425300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1425200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1440000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1061400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>958100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>999500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>928400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4639,228 +4744,237 @@
       <c r="AL47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="3">
         <v>3836000</v>
       </c>
-      <c r="E48" s="3">
-        <v>3670300</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="3">
         <v>4013100</v>
       </c>
-      <c r="G48" s="3">
-        <v>3609300</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" s="3">
         <v>3710000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3888800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3619500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3659300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3907400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3605300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3256300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3416200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6289100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3037000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3209100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3284500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3199400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3395700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3631100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4025000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4251400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4416300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4465200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4457200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4667300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4563000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4490400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4389800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4337400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4329700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4294800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4198900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4096900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3997600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3936200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3">
         <v>505900</v>
       </c>
-      <c r="E49" s="3">
-        <v>456300</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="3">
         <v>493000</v>
       </c>
-      <c r="G49" s="3">
-        <v>438800</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3">
         <v>460300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>483300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>456000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>475000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>498400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>442300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>395500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>415200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>411300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>151800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>159400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>162400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>159000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>161900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>173300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>187600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>188200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>172900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>172200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>163500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>161400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>153300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>149800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>147200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>146200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>139900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>140700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>135000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>135600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>129900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,25 +5196,28 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>226900</v>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E52" s="3">
-        <v>200300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -5112,85 +5232,88 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>1042100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>953200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>998300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2702900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1706800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1826200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1903300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1457600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1421800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1488900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1726200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1735300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1816600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1839200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1865000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1936100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1603200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1588900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1530100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1599800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1276700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1362600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1339200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1304700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1350000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1345100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3">
         <v>20146900</v>
       </c>
-      <c r="E54" s="3">
-        <v>19372700</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="3">
         <v>19678600</v>
       </c>
-      <c r="G54" s="3">
-        <v>17501400</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="3">
         <v>17719600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18893100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17116000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17157900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18488300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17298800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14877100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15143900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14439500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14053900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13987200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14360900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13919600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14965300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15415400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17173200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17248600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18707700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17918500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17509700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17671400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18892700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17656100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16797100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16136700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>17206800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16230400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15657000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14966900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15952000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>14698300</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
         <v>3965800</v>
       </c>
-      <c r="E57" s="3">
-        <v>3548900</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="3">
         <v>3596000</v>
       </c>
-      <c r="G57" s="3">
-        <v>3184200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3">
         <v>3449400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3380300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3055800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3021200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3402100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3075300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2538500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2548400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4941500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2174500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2173700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2313900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2518000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2447800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2367500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2621900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3274500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3083100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2942400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3095300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3558300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3258700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3116400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3052900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3283100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3120100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2995600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2794300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3033700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2805600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2587400</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3">
         <v>3520600</v>
       </c>
-      <c r="E58" s="3">
-        <v>4757600</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="3">
         <v>4455100</v>
       </c>
-      <c r="G58" s="3">
-        <v>3355300</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I58" s="3">
         <v>2999500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4058200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3151500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2834200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2559000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2930600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2317200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2187200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3378000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1223400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1279500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1016400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1224000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1345800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1415400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1634900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1653900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2582000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1721200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1287200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1060400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2197400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1264300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1106800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2153700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1639000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>976200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1162300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1079000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1467300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>994200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
         <v>4849700</v>
       </c>
-      <c r="E59" s="3">
-        <v>3881700</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3">
         <v>3957500</v>
       </c>
-      <c r="G59" s="3">
-        <v>3921800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
         <v>3742400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3641500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3705400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3457400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3883400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3239200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2885200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3042600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4901600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3758300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3306200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3568900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2763500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3549100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3645000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3728900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3421000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4249500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4400600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4389200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3687000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4536000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4683500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4229300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3591100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4206100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3979900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4074200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3368600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4169500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4018400</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="3">
         <v>12336100</v>
       </c>
-      <c r="E60" s="3">
-        <v>12188200</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="3">
         <v>12008600</v>
       </c>
-      <c r="G60" s="3">
-        <v>10461300</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="3">
         <v>10191300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11080000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9912700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9312700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9844400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9245000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7741000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7778200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7036600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7156200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6759400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6899100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6505500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7342700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7428000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7985700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8349500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9914600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8771700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8305700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9064200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8389000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7859400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8965300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7951700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8030800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7481300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8442400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7599900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>2419500</v>
       </c>
-      <c r="E61" s="3">
-        <v>2175300</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>2384300</v>
       </c>
-      <c r="G61" s="3">
-        <v>2239100</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>2588600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2833100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2556700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2888900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3348100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3054400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2760600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2896400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2978600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2553900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2705600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2831300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2826800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2831300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3012800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3572900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3081100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3024000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3087500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2996100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3162500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2995400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2840900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2830800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2853800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2937100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3077200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2508500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2475100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2627400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2454600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3">
         <v>94500</v>
       </c>
-      <c r="E62" s="3">
-        <v>113500</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3">
         <v>125300</v>
       </c>
-      <c r="G62" s="3">
-        <v>112300</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3">
         <v>114300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>118100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>110800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>809400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>844300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1233200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1200600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1262100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1277500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1164400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1444200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1537400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1711600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1663500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1441800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1418300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1393600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1472600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1362100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1360700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1236500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1071800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1087100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1076900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1043000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1007200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1080700</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3">
         <v>15305000</v>
       </c>
-      <c r="E66" s="3">
-        <v>14982000</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="3">
         <v>15058100</v>
       </c>
-      <c r="G66" s="3">
-        <v>13287900</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="3">
         <v>13392100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14712400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13221100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12971800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13998300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13330600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11429100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11640400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11083100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11040200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10858200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11138400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10620400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11739800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12100800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13401500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13234500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14525700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13713800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13304000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13093300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14506700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13411300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12591200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11923500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13128900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12237000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11710700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11088500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12292600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11247600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3">
         <v>3229000</v>
       </c>
-      <c r="E72" s="3">
-        <v>2750500</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="3">
         <v>2887000</v>
       </c>
-      <c r="G72" s="3">
-        <v>2584600</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I72" s="3">
         <v>2678600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2505100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2322000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2623500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2860500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2593700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2180400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2178900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2129300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1860900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1957200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2034500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2173600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2286100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2332000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2685700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2877600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2848900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2849600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2798900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3119500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2912600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2781500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2777500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2784400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2654300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2621100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2598000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2549700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2476700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2315100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3">
         <v>4694000</v>
       </c>
-      <c r="E76" s="3">
-        <v>4247400</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="3">
         <v>4466900</v>
       </c>
-      <c r="G76" s="3">
-        <v>4083000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" s="3">
         <v>4192200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4035000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3761500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4044500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4334500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3968200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3448000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3503500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3356400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3013700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3128900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3222500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3299200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3225400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3314600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3771700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4014100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4182100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4204800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4205800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4578100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4386000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4244700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4205900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4213200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4078000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3993400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3946300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3878400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3659400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3450600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,123 +7918,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7876,86 +8071,89 @@
       <c r="L81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N81" s="3">
         <v>204100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>116800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>22800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>80700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>97500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-120700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>122500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>77400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>41500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-75600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>154400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>141400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-57200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>130100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>33100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>68500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>73000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>161600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-44700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3">
         <v>132000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>124100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>148200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>147900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>160900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>139500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>128400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>139900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N83" s="3">
         <v>130700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>118500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>128100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>133000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>130100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>139400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>137300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>112000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>111700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>118200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>128300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>139600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>139400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>141400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>135100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>143800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>139000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>136000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>133600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>130900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>128500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>125300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>122800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>119500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>115100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,67 +8868,70 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
         <v>1516800</v>
       </c>
-      <c r="E89" s="3">
-        <v>-262300</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="3">
         <v>-422800</v>
       </c>
-      <c r="G89" s="3">
-        <v>146800</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" s="3">
         <v>856700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-585100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-155200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1028600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-305900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-51300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-417800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1942400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-353600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-393600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-217400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -8764,8 +8981,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,67 +9024,68 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
         <v>-208400</v>
       </c>
-      <c r="E91" s="3">
-        <v>-153500</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="3">
         <v>-144500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-140700</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="3">
         <v>-77400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-195800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-145500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-131500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-151900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14756000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10678000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13315000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25250000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13164000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15209000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-103000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8914,8 +9135,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,67 +9361,70 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
         <v>-208900</v>
       </c>
-      <c r="E94" s="3">
-        <v>-191700</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="3">
         <v>-165100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-162400</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I94" s="3">
         <v>-57600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-234200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-174800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-152100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-182000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-126500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-72800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-162000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-125500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-105300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-99800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -9244,8 +9474,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,13 +9517,14 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>4100</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>10</v>
@@ -9316,30 +9550,30 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3">
         <v>-32900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-20800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-21300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -9394,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,67 +9967,70 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1299300</v>
       </c>
-      <c r="E100" s="3">
-        <v>510600</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="3">
         <v>675500</v>
       </c>
-      <c r="G100" s="3">
-        <v>168600</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I100" s="3">
         <v>-884800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>916200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>105000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-498400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>428500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>181500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>423100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1541200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>510300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>128200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>277100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -9834,67 +10080,70 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3">
         <v>-32400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-20300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-28000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>41800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-30700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-49700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N101" s="3">
         <v>39100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-45500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2600</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -9944,67 +10193,70 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>24900</v>
       </c>
-      <c r="E102" s="3">
-        <v>10500</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>171300</v>
       </c>
-      <c r="G102" s="3">
-        <v>116300</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-118100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>117800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-321900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>379300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>35200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>29000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-202300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>264600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>95400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-449100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-37500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -10052,6 +10304,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
